--- a/datasets/20261021_recontrataciones_concentrado.xlsx
+++ b/datasets/20261021_recontrataciones_concentrado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INE\Documents\reductor_dias\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8F40CE-88D7-410F-B131-DF00AD2FB588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD83CD8-9034-43C3-B52A-02FDA8956359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="284">
   <si>
     <t>Distrito</t>
   </si>
@@ -647,9 +647,6 @@
     <t>Paraíso</t>
   </si>
   <si>
-    <t>Ranchería Ixtacomitán 1ra Sección</t>
-  </si>
-  <si>
     <t>Nuevo Laredo</t>
   </si>
   <si>
@@ -659,15 +656,9 @@
     <t>Río Bravo</t>
   </si>
   <si>
-    <t>H. Matamoros</t>
-  </si>
-  <si>
     <t>Ciudad Victoria</t>
   </si>
   <si>
-    <t>Ciudad Mante</t>
-  </si>
-  <si>
     <t>Tampico</t>
   </si>
   <si>
@@ -906,6 +897,18 @@
   </si>
   <si>
     <t>22</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Matamoros</t>
+  </si>
+  <si>
+    <t>El Mante</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1281,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1399,6 +1402,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2283,7 +2292,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>27</v>
@@ -2311,7 +2320,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>27</v>
@@ -2339,7 +2348,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>27</v>
@@ -2367,7 +2376,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>25</v>
@@ -2395,7 +2404,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>27</v>
@@ -2423,10 +2432,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E24" s="16"/>
       <c r="F24" s="11"/>
@@ -2504,7 +2513,7 @@
     </row>
     <row r="27" spans="2:21" ht="28" x14ac:dyDescent="0.35">
       <c r="B27" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>12</v>
@@ -2532,7 +2541,7 @@
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B28" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>22</v>
@@ -2560,7 +2569,7 @@
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B29" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>12</v>
@@ -2588,7 +2597,7 @@
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B30" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>22</v>
@@ -2616,7 +2625,7 @@
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B31" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>23</v>
@@ -2644,10 +2653,10 @@
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B32" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>35</v>
@@ -2672,10 +2681,10 @@
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B33" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>36</v>
@@ -2700,10 +2709,10 @@
     </row>
     <row r="34" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B34" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>36</v>
@@ -2728,10 +2737,10 @@
     </row>
     <row r="35" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B35" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>35</v>
@@ -2756,10 +2765,10 @@
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B36" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>230</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>233</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>37</v>
@@ -2784,7 +2793,7 @@
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B37" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C37" s="19" t="s">
         <v>12</v>
@@ -2812,7 +2821,7 @@
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B38" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C38" s="19" t="s">
         <v>22</v>
@@ -2840,7 +2849,7 @@
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B39" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>12</v>
@@ -2868,7 +2877,7 @@
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B40" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>22</v>
@@ -2896,7 +2905,7 @@
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B41" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>23</v>
@@ -2924,10 +2933,10 @@
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B42" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>43</v>
@@ -2952,10 +2961,10 @@
     </row>
     <row r="43" spans="2:21" ht="28" x14ac:dyDescent="0.35">
       <c r="B43" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>44</v>
@@ -2980,10 +2989,10 @@
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B44" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>45</v>
@@ -3008,10 +3017,10 @@
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B45" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>46</v>
@@ -3036,10 +3045,10 @@
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B46" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>47</v>
@@ -3064,10 +3073,10 @@
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B47" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>45</v>
@@ -3092,10 +3101,10 @@
     </row>
     <row r="48" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B48" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>232</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>235</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>48</v>
@@ -3120,10 +3129,10 @@
     </row>
     <row r="49" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B49" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>49</v>
@@ -3148,10 +3157,10 @@
     </row>
     <row r="50" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B50" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>50</v>
@@ -3176,10 +3185,10 @@
     </row>
     <row r="51" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B51" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>51</v>
@@ -3204,7 +3213,7 @@
     </row>
     <row r="52" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B52" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C52" s="19" t="s">
         <v>12</v>
@@ -3232,7 +3241,7 @@
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B53" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>22</v>
@@ -3260,7 +3269,7 @@
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B54" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C54" s="19" t="s">
         <v>23</v>
@@ -3288,10 +3297,10 @@
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B55" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>52</v>
@@ -3316,13 +3325,13 @@
     </row>
     <row r="56" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B56" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -3344,10 +3353,10 @@
     </row>
     <row r="57" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B57" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>53</v>
@@ -3372,10 +3381,10 @@
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B58" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>54</v>
@@ -3400,10 +3409,10 @@
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B59" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>53</v>
@@ -3428,10 +3437,10 @@
     </row>
     <row r="60" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B60" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>55</v>
@@ -3455,13 +3464,13 @@
       <c r="U60" s="10"/>
     </row>
     <row r="61" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B61" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C61" s="44" t="s">
+      <c r="B61" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D61" s="45" t="s">
+      <c r="D61" s="47" t="s">
         <v>56</v>
       </c>
       <c r="E61" s="10"/>
@@ -3483,13 +3492,13 @@
       <c r="U61" s="10"/>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B62" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C62" s="44" t="s">
+      <c r="B62" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C62" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="45" t="s">
+      <c r="D62" s="47" t="s">
         <v>56</v>
       </c>
       <c r="E62" s="10"/>
@@ -3511,13 +3520,13 @@
       <c r="U62" s="10"/>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B63" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C63" s="44" t="s">
+      <c r="B63" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C63" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="45" t="s">
+      <c r="D63" s="47" t="s">
         <v>57</v>
       </c>
       <c r="E63" s="10"/>
@@ -3539,13 +3548,13 @@
       <c r="U63" s="10"/>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B64" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C64" s="44" t="s">
-        <v>229</v>
-      </c>
-      <c r="D64" s="45" t="s">
+      <c r="B64" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D64" s="47" t="s">
         <v>58</v>
       </c>
       <c r="E64" s="10"/>
@@ -3567,14 +3576,14 @@
       <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B65" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C65" s="44" t="s">
-        <v>230</v>
-      </c>
-      <c r="D65" s="45" t="s">
-        <v>272</v>
+      <c r="B65" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C65" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="D65" s="47" t="s">
+        <v>269</v>
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
@@ -3595,13 +3604,13 @@
       <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:21" ht="28" x14ac:dyDescent="0.35">
-      <c r="B66" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C66" s="44" t="s">
+      <c r="B66" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="D66" s="45" t="s">
+      <c r="C66" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D66" s="47" t="s">
         <v>60</v>
       </c>
       <c r="E66" s="10"/>
@@ -3623,13 +3632,13 @@
       <c r="U66" s="10"/>
     </row>
     <row r="67" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B67" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C67" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="D67" s="45" t="s">
+      <c r="B67" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="D67" s="47" t="s">
         <v>56</v>
       </c>
       <c r="E67" s="10"/>
@@ -3651,13 +3660,13 @@
       <c r="U67" s="10"/>
     </row>
     <row r="68" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B68" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C68" s="44" t="s">
-        <v>233</v>
-      </c>
-      <c r="D68" s="45" t="s">
+      <c r="B68" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C68" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="D68" s="47" t="s">
         <v>61</v>
       </c>
       <c r="E68" s="10"/>
@@ -3679,13 +3688,13 @@
       <c r="U68" s="10"/>
     </row>
     <row r="69" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B69" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C69" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="D69" s="45" t="s">
+      <c r="B69" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="D69" s="47" t="s">
         <v>62</v>
       </c>
       <c r="E69" s="10"/>
@@ -3707,13 +3716,13 @@
       <c r="U69" s="10"/>
     </row>
     <row r="70" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B70" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C70" s="44" t="s">
-        <v>235</v>
-      </c>
-      <c r="D70" s="45" t="s">
+      <c r="B70" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="D70" s="47" t="s">
         <v>63</v>
       </c>
       <c r="E70" s="10"/>
@@ -3735,13 +3744,13 @@
       <c r="U70" s="10"/>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B71" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C71" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="48" t="s">
+      <c r="B71" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C71" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="D71" s="50" t="s">
         <v>64</v>
       </c>
       <c r="E71" s="10"/>
@@ -3763,13 +3772,13 @@
       <c r="U71" s="10"/>
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B72" s="44" t="s">
+      <c r="B72" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" s="46" t="s">
         <v>234</v>
       </c>
-      <c r="C72" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="D72" s="45" t="s">
+      <c r="D72" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E72" s="10"/>
@@ -3791,13 +3800,13 @@
       <c r="U72" s="10"/>
     </row>
     <row r="73" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B73" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C73" s="44" t="s">
-        <v>238</v>
-      </c>
-      <c r="D73" s="45" t="s">
+      <c r="B73" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C73" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="D73" s="47" t="s">
         <v>65</v>
       </c>
       <c r="E73" s="10"/>
@@ -3819,13 +3828,13 @@
       <c r="U73" s="10"/>
     </row>
     <row r="74" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B74" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C74" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="D74" s="45" t="s">
+      <c r="B74" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C74" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="D74" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E74" s="10"/>
@@ -3847,13 +3856,13 @@
       <c r="U74" s="10"/>
     </row>
     <row r="75" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B75" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C75" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="D75" s="45" t="s">
+      <c r="B75" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C75" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="D75" s="47" t="s">
         <v>66</v>
       </c>
       <c r="E75" s="10"/>
@@ -3875,14 +3884,14 @@
       <c r="U75" s="10"/>
     </row>
     <row r="76" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B76" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C76" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="D76" s="45" t="s">
-        <v>276</v>
+      <c r="B76" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76" s="47" t="s">
+        <v>273</v>
       </c>
       <c r="E76" s="10"/>
       <c r="F76" s="10"/>
@@ -3903,14 +3912,14 @@
       <c r="U76" s="10"/>
     </row>
     <row r="77" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B77" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C77" s="44" t="s">
-        <v>277</v>
-      </c>
-      <c r="D77" s="45" t="s">
-        <v>278</v>
+      <c r="B77" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C77" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>275</v>
       </c>
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
@@ -3931,13 +3940,13 @@
       <c r="U77" s="10"/>
     </row>
     <row r="78" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B78" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C78" s="44" t="s">
-        <v>279</v>
-      </c>
-      <c r="D78" s="45" t="s">
+      <c r="B78" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="D78" s="47" t="s">
         <v>58</v>
       </c>
       <c r="E78" s="10"/>
@@ -3959,13 +3968,13 @@
       <c r="U78" s="10"/>
     </row>
     <row r="79" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B79" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C79" s="44" t="s">
-        <v>280</v>
-      </c>
-      <c r="D79" s="45" t="s">
+      <c r="B79" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C79" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="D79" s="47" t="s">
         <v>61</v>
       </c>
       <c r="E79" s="10"/>
@@ -3987,13 +3996,13 @@
       <c r="U79" s="10"/>
     </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B80" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C80" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="D80" s="45" t="s">
+      <c r="B80" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C80" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" s="47" t="s">
         <v>58</v>
       </c>
       <c r="E80" s="10"/>
@@ -4015,13 +4024,13 @@
       <c r="U80" s="10"/>
     </row>
     <row r="81" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B81" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C81" s="46">
+      <c r="B81" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C81" s="48">
         <v>21</v>
       </c>
-      <c r="D81" s="47" t="s">
+      <c r="D81" s="49" t="s">
         <v>67</v>
       </c>
       <c r="E81" s="10"/>
@@ -4043,13 +4052,13 @@
       <c r="U81" s="10"/>
     </row>
     <row r="82" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B82" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="C82" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="D82" s="45" t="s">
+      <c r="B82" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="46" t="s">
+        <v>279</v>
+      </c>
+      <c r="D82" s="47" t="s">
         <v>58</v>
       </c>
       <c r="E82" s="10"/>
@@ -5170,7 +5179,7 @@
         <v>6</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
@@ -5450,7 +5459,7 @@
         <v>16</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
@@ -5506,7 +5515,7 @@
         <v>18</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
@@ -5534,7 +5543,7 @@
         <v>19</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
@@ -5590,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
@@ -5674,7 +5683,7 @@
         <v>4</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
@@ -5702,7 +5711,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
@@ -5730,7 +5739,7 @@
         <v>6</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
@@ -5786,7 +5795,7 @@
         <v>8</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
@@ -6738,7 +6747,7 @@
         <v>22</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
@@ -6766,7 +6775,7 @@
         <v>23</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
@@ -6791,10 +6800,10 @@
         <v>16</v>
       </c>
       <c r="C180" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
@@ -6819,10 +6828,10 @@
         <v>16</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E181" s="10"/>
       <c r="F181" s="10"/>
@@ -6847,10 +6856,10 @@
         <v>16</v>
       </c>
       <c r="C182" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
@@ -6875,7 +6884,7 @@
         <v>16</v>
       </c>
       <c r="C183" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D183" s="14" t="s">
         <v>135</v>
@@ -6903,7 +6912,7 @@
         <v>16</v>
       </c>
       <c r="C184" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D184" s="14" t="s">
         <v>136</v>
@@ -6931,10 +6940,10 @@
         <v>16</v>
       </c>
       <c r="C185" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E185" s="10"/>
       <c r="F185" s="10"/>
@@ -6959,7 +6968,7 @@
         <v>16</v>
       </c>
       <c r="C186" s="19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D186" s="14" t="s">
         <v>136</v>
@@ -6987,7 +6996,7 @@
         <v>16</v>
       </c>
       <c r="C187" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D187" s="14" t="s">
         <v>137</v>
@@ -7099,7 +7108,7 @@
         <v>17</v>
       </c>
       <c r="C191" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D191" s="14" t="s">
         <v>141</v>
@@ -7127,7 +7136,7 @@
         <v>17</v>
       </c>
       <c r="C192" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D192" s="14" t="s">
         <v>142</v>
@@ -7298,7 +7307,7 @@
         <v>23</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
@@ -7323,7 +7332,7 @@
         <v>19</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D199" s="14" t="s">
         <v>148</v>
@@ -7351,7 +7360,7 @@
         <v>19</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D200" s="14" t="s">
         <v>149</v>
@@ -7379,7 +7388,7 @@
         <v>19</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D201" s="14" t="s">
         <v>149</v>
@@ -7407,10 +7416,10 @@
         <v>19</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D202" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
@@ -7435,7 +7444,7 @@
         <v>19</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D203" s="14" t="s">
         <v>150</v>
@@ -7463,7 +7472,7 @@
         <v>19</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D204" s="14" t="s">
         <v>151</v>
@@ -7690,7 +7699,7 @@
         <v>3</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
@@ -7774,7 +7783,7 @@
         <v>6</v>
       </c>
       <c r="D215" s="14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
@@ -7858,7 +7867,7 @@
         <v>9</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -7914,7 +7923,7 @@
         <v>1</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
@@ -7970,7 +7979,7 @@
         <v>3</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
@@ -8026,7 +8035,7 @@
         <v>5</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
@@ -8054,7 +8063,7 @@
         <v>6</v>
       </c>
       <c r="D225" s="14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
@@ -8138,7 +8147,7 @@
         <v>9</v>
       </c>
       <c r="D228" s="14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
@@ -8166,7 +8175,7 @@
         <v>10</v>
       </c>
       <c r="D229" s="14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -8194,7 +8203,7 @@
         <v>11</v>
       </c>
       <c r="D230" s="14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -8222,7 +8231,7 @@
         <v>12</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
@@ -8641,7 +8650,7 @@
       <c r="C246" s="19">
         <v>1</v>
       </c>
-      <c r="D246" s="43" t="s">
+      <c r="D246" s="45" t="s">
         <v>179</v>
       </c>
       <c r="E246" s="10"/>
@@ -8669,7 +8678,7 @@
       <c r="C247" s="19">
         <v>2</v>
       </c>
-      <c r="D247" s="43" t="s">
+      <c r="D247" s="45" t="s">
         <v>176</v>
       </c>
       <c r="E247" s="10"/>
@@ -8697,7 +8706,7 @@
       <c r="C248" s="19">
         <v>3</v>
       </c>
-      <c r="D248" s="43" t="s">
+      <c r="D248" s="45" t="s">
         <v>177</v>
       </c>
       <c r="E248" s="10"/>
@@ -8725,7 +8734,7 @@
       <c r="C249" s="19">
         <v>4</v>
       </c>
-      <c r="D249" s="43" t="s">
+      <c r="D249" s="45" t="s">
         <v>178</v>
       </c>
       <c r="E249" s="10"/>
@@ -8753,7 +8762,7 @@
       <c r="C250" s="19">
         <v>5</v>
       </c>
-      <c r="D250" s="43" t="s">
+      <c r="D250" s="45" t="s">
         <v>179</v>
       </c>
       <c r="E250" s="10"/>
@@ -8781,7 +8790,7 @@
       <c r="C251" s="19">
         <v>6</v>
       </c>
-      <c r="D251" s="43" t="s">
+      <c r="D251" s="45" t="s">
         <v>179</v>
       </c>
       <c r="E251" s="10"/>
@@ -8809,7 +8818,7 @@
       <c r="C252" s="19">
         <v>7</v>
       </c>
-      <c r="D252" s="43" t="s">
+      <c r="D252" s="45" t="s">
         <v>180</v>
       </c>
       <c r="E252" s="10"/>
@@ -8950,7 +8959,7 @@
         <v>5</v>
       </c>
       <c r="D257" s="14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E257" s="10"/>
       <c r="F257" s="10"/>
@@ -9006,7 +9015,7 @@
         <v>7</v>
       </c>
       <c r="D259" s="14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E259" s="10"/>
       <c r="F259" s="10"/>
@@ -9223,13 +9232,13 @@
       <c r="U266" s="10"/>
     </row>
     <row r="267" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B267" s="19">
-        <v>27</v>
-      </c>
-      <c r="C267" s="19">
-        <v>1</v>
-      </c>
-      <c r="D267" s="14" t="s">
+      <c r="B267" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C267" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D267" s="47" t="s">
         <v>191</v>
       </c>
       <c r="E267" s="10"/>
@@ -9251,13 +9260,13 @@
       <c r="U267" s="10"/>
     </row>
     <row r="268" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B268" s="19">
-        <v>27</v>
-      </c>
-      <c r="C268" s="19">
-        <v>2</v>
-      </c>
-      <c r="D268" s="14" t="s">
+      <c r="B268" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C268" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D268" s="47" t="s">
         <v>192</v>
       </c>
       <c r="E268" s="10"/>
@@ -9279,13 +9288,13 @@
       <c r="U268" s="10"/>
     </row>
     <row r="269" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B269" s="19">
-        <v>27</v>
-      </c>
-      <c r="C269" s="19">
-        <v>3</v>
-      </c>
-      <c r="D269" s="14" t="s">
+      <c r="B269" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C269" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D269" s="47" t="s">
         <v>193</v>
       </c>
       <c r="E269" s="10"/>
@@ -9307,13 +9316,13 @@
       <c r="U269" s="10"/>
     </row>
     <row r="270" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B270" s="19">
-        <v>27</v>
-      </c>
-      <c r="C270" s="19">
-        <v>4</v>
-      </c>
-      <c r="D270" s="14" t="s">
+      <c r="B270" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C270" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D270" s="47" t="s">
         <v>194</v>
       </c>
       <c r="E270" s="10"/>
@@ -9335,13 +9344,13 @@
       <c r="U270" s="10"/>
     </row>
     <row r="271" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B271" s="19">
-        <v>27</v>
-      </c>
-      <c r="C271" s="19">
-        <v>5</v>
-      </c>
-      <c r="D271" s="14" t="s">
+      <c r="B271" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C271" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="D271" s="47" t="s">
         <v>195</v>
       </c>
       <c r="E271" s="10"/>
@@ -9362,15 +9371,15 @@
       <c r="T271" s="10"/>
       <c r="U271" s="10"/>
     </row>
-    <row r="272" spans="2:21" ht="28" x14ac:dyDescent="0.35">
-      <c r="B272" s="19">
-        <v>27</v>
-      </c>
-      <c r="C272" s="19">
-        <v>6</v>
-      </c>
-      <c r="D272" s="14" t="s">
-        <v>196</v>
+    <row r="272" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B272" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C272" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D272" s="47" t="s">
+        <v>194</v>
       </c>
       <c r="E272" s="10"/>
       <c r="F272" s="10"/>
@@ -9391,14 +9400,14 @@
       <c r="U272" s="10"/>
     </row>
     <row r="273" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B273" s="19">
-        <v>28</v>
-      </c>
-      <c r="C273" s="19">
-        <v>1</v>
-      </c>
-      <c r="D273" s="14" t="s">
-        <v>197</v>
+      <c r="B273" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C273" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D273" s="47" t="s">
+        <v>196</v>
       </c>
       <c r="E273" s="10"/>
       <c r="F273" s="10"/>
@@ -9419,14 +9428,14 @@
       <c r="U273" s="10"/>
     </row>
     <row r="274" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B274" s="19">
-        <v>28</v>
-      </c>
-      <c r="C274" s="19">
-        <v>2</v>
-      </c>
-      <c r="D274" s="14" t="s">
-        <v>198</v>
+      <c r="B274" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C274" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D274" s="47" t="s">
+        <v>197</v>
       </c>
       <c r="E274" s="10"/>
       <c r="F274" s="10"/>
@@ -9447,14 +9456,14 @@
       <c r="U274" s="10"/>
     </row>
     <row r="275" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B275" s="19">
-        <v>28</v>
-      </c>
-      <c r="C275" s="19">
-        <v>3</v>
-      </c>
-      <c r="D275" s="14" t="s">
-        <v>199</v>
+      <c r="B275" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C275" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D275" s="47" t="s">
+        <v>198</v>
       </c>
       <c r="E275" s="10"/>
       <c r="F275" s="10"/>
@@ -9475,14 +9484,14 @@
       <c r="U275" s="10"/>
     </row>
     <row r="276" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B276" s="19">
-        <v>28</v>
-      </c>
-      <c r="C276" s="19">
-        <v>4</v>
-      </c>
-      <c r="D276" s="14" t="s">
-        <v>200</v>
+      <c r="B276" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="C276" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D276" s="44" t="s">
+        <v>281</v>
       </c>
       <c r="E276" s="10"/>
       <c r="F276" s="10"/>
@@ -9503,14 +9512,14 @@
       <c r="U276" s="10"/>
     </row>
     <row r="277" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B277" s="19">
-        <v>28</v>
-      </c>
-      <c r="C277" s="19">
-        <v>5</v>
-      </c>
-      <c r="D277" s="14" t="s">
-        <v>201</v>
+      <c r="B277" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C277" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="D277" s="47" t="s">
+        <v>199</v>
       </c>
       <c r="E277" s="10"/>
       <c r="F277" s="10"/>
@@ -9531,14 +9540,14 @@
       <c r="U277" s="10"/>
     </row>
     <row r="278" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B278" s="19">
-        <v>28</v>
-      </c>
-      <c r="C278" s="19">
-        <v>6</v>
-      </c>
-      <c r="D278" s="14" t="s">
-        <v>202</v>
+      <c r="B278" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C278" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D278" s="47" t="s">
+        <v>282</v>
       </c>
       <c r="E278" s="10"/>
       <c r="F278" s="10"/>
@@ -9559,14 +9568,14 @@
       <c r="U278" s="10"/>
     </row>
     <row r="279" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B279" s="19">
-        <v>28</v>
-      </c>
-      <c r="C279" s="19">
-        <v>7</v>
-      </c>
-      <c r="D279" s="14" t="s">
-        <v>198</v>
+      <c r="B279" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="C279" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="D279" s="44" t="s">
+        <v>197</v>
       </c>
       <c r="E279" s="10"/>
       <c r="F279" s="10"/>
@@ -9587,14 +9596,14 @@
       <c r="U279" s="10"/>
     </row>
     <row r="280" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B280" s="19">
-        <v>28</v>
-      </c>
-      <c r="C280" s="19">
-        <v>8</v>
-      </c>
-      <c r="D280" s="14" t="s">
-        <v>203</v>
+      <c r="B280" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C280" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="D280" s="47" t="s">
+        <v>200</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="10"/>
@@ -9622,7 +9631,7 @@
         <v>12</v>
       </c>
       <c r="D281" s="14" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E281" s="10"/>
       <c r="F281" s="10"/>
@@ -9650,7 +9659,7 @@
         <v>22</v>
       </c>
       <c r="D282" s="14" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E282" s="10"/>
       <c r="F282" s="10"/>
@@ -9678,7 +9687,7 @@
         <v>23</v>
       </c>
       <c r="D283" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E283" s="10"/>
       <c r="F283" s="10"/>
@@ -9706,7 +9715,7 @@
         <v>1</v>
       </c>
       <c r="D284" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E284" s="10"/>
       <c r="F284" s="10"/>
@@ -9734,7 +9743,7 @@
         <v>2</v>
       </c>
       <c r="D285" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E285" s="10"/>
       <c r="F285" s="10"/>
@@ -9762,7 +9771,7 @@
         <v>3</v>
       </c>
       <c r="D286" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E286" s="10"/>
       <c r="F286" s="10"/>
@@ -9790,7 +9799,7 @@
         <v>4</v>
       </c>
       <c r="D287" s="14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E287" s="10"/>
       <c r="F287" s="10"/>
@@ -9818,7 +9827,7 @@
         <v>5</v>
       </c>
       <c r="D288" s="14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E288" s="10"/>
       <c r="F288" s="10"/>
@@ -9846,7 +9855,7 @@
         <v>6</v>
       </c>
       <c r="D289" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E289" s="10"/>
       <c r="F289" s="10"/>
@@ -9874,7 +9883,7 @@
         <v>7</v>
       </c>
       <c r="D290" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E290" s="10"/>
       <c r="F290" s="10"/>
@@ -9902,7 +9911,7 @@
         <v>8</v>
       </c>
       <c r="D291" s="14" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E291" s="10"/>
       <c r="F291" s="10"/>
@@ -9930,7 +9939,7 @@
         <v>9</v>
       </c>
       <c r="D292" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E292" s="10"/>
       <c r="F292" s="10"/>
@@ -9958,7 +9967,7 @@
         <v>10</v>
       </c>
       <c r="D293" s="14" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E293" s="10"/>
       <c r="F293" s="10"/>
@@ -9986,7 +9995,7 @@
         <v>11</v>
       </c>
       <c r="D294" s="14" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E294" s="10"/>
       <c r="F294" s="10"/>
@@ -10014,7 +10023,7 @@
         <v>12</v>
       </c>
       <c r="D295" s="14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="10"/>
@@ -10042,7 +10051,7 @@
         <v>13</v>
       </c>
       <c r="D296" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E296" s="10"/>
       <c r="F296" s="10"/>
@@ -10070,7 +10079,7 @@
         <v>14</v>
       </c>
       <c r="D297" s="14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E297" s="10"/>
       <c r="F297" s="10"/>
@@ -10098,7 +10107,7 @@
         <v>15</v>
       </c>
       <c r="D298" s="14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E298" s="10"/>
       <c r="F298" s="10"/>
@@ -10126,7 +10135,7 @@
         <v>16</v>
       </c>
       <c r="D299" s="14" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E299" s="10"/>
       <c r="F299" s="10"/>
@@ -10154,7 +10163,7 @@
         <v>17</v>
       </c>
       <c r="D300" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E300" s="10"/>
       <c r="F300" s="10"/>
@@ -10182,7 +10191,7 @@
         <v>18</v>
       </c>
       <c r="D301" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E301" s="10"/>
       <c r="F301" s="10"/>
@@ -10210,7 +10219,7 @@
         <v>19</v>
       </c>
       <c r="D302" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E302" s="10"/>
       <c r="F302" s="10"/>
@@ -10238,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="D303" s="14" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E303" s="10"/>
       <c r="F303" s="10"/>
@@ -10266,7 +10275,7 @@
         <v>2</v>
       </c>
       <c r="D304" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E304" s="10"/>
       <c r="F304" s="10"/>
@@ -10294,7 +10303,7 @@
         <v>3</v>
       </c>
       <c r="D305" s="14" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E305" s="10"/>
       <c r="F305" s="10"/>
@@ -10322,7 +10331,7 @@
         <v>4</v>
       </c>
       <c r="D306" s="14" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E306" s="10"/>
       <c r="F306" s="10"/>
@@ -10350,7 +10359,7 @@
         <v>5</v>
       </c>
       <c r="D307" s="14" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E307" s="10"/>
       <c r="F307" s="10"/>
@@ -10378,7 +10387,7 @@
         <v>6</v>
       </c>
       <c r="D308" s="14" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E308" s="10"/>
       <c r="F308" s="10"/>
@@ -10406,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="D309" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E309" s="10"/>
       <c r="F309" s="10"/>
@@ -10434,7 +10443,7 @@
         <v>2</v>
       </c>
       <c r="D310" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E310" s="10"/>
       <c r="F310" s="10"/>
@@ -10462,7 +10471,7 @@
         <v>3</v>
       </c>
       <c r="D311" s="14" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E311" s="10"/>
       <c r="F311" s="10"/>

--- a/datasets/20261021_recontrataciones_concentrado.xlsx
+++ b/datasets/20261021_recontrataciones_concentrado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INE\Documents\reductor_dias\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFA18DF-30CD-400E-9365-A5C83FAA725E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7EB79B-C6F8-4BFA-A2A0-AD0924ABDB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="284">
   <si>
     <t>Distrito</t>
   </si>
@@ -50,31 +50,10 @@
     <t>Cabecera</t>
   </si>
   <si>
-    <t>Fecha de corte:</t>
-  </si>
-  <si>
     <t>Proceso Electoral Concurrente 2026-2027</t>
   </si>
   <si>
-    <t>Vocalía de Capacitación Electoral y Educación Cívica</t>
-  </si>
-  <si>
     <t>A dos digitos</t>
-  </si>
-  <si>
-    <r>
-      <t>Junta Local Ejecutiva en</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Nombre de la entidad)</t>
-    </r>
   </si>
   <si>
     <t>Reporte sobre el avance del proceso de recontratación</t>
@@ -118,9 +97,6 @@
     <t>Total de personas contactadas</t>
   </si>
   <si>
-    <t>Nota: en los casos de las personas que hayan participado en más de un proceso electoral, únicamente se deberá registrar su participación en el más reciente, con el fin de evitar duplicidades.</t>
-  </si>
-  <si>
     <t>Observaciones 
 (en su caso)</t>
   </si>
@@ -912,6 +888,15 @@
   </si>
   <si>
     <t>Proyección SE y CAE 2026 - 2027</t>
+  </si>
+  <si>
+    <t>Dirección Ejecutiva de Capacitación Electoral y Educación Cívica</t>
+  </si>
+  <si>
+    <t>Fecha de corte: 20 de octubre de 2026.</t>
+  </si>
+  <si>
+    <t>Nota: en los casos de las personas que hayan participado en más de un proceso electoral, únicamente se registró su participación en el más reciente, con el fin de evitar duplicidades.</t>
   </si>
 </sst>
 </file>
@@ -921,7 +906,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -972,13 +957,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
       <color rgb="FFFF0000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
@@ -1062,7 +1040,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1082,32 +1060,6 @@
       </top>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1147,17 +1099,6 @@
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1317,21 +1258,21 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1340,53 +1281,89 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1394,75 +1371,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1868,7 +1803,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD312"/>
+  <dimension ref="A2:XFC312"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.7265625" customWidth="1"/>
@@ -1887,50 +1822,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.3">
-      <c r="C2" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
+      <c r="C2" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
     </row>
     <row r="3" spans="2:22" s="3" customFormat="1" ht="20" x14ac:dyDescent="0.3">
-      <c r="C3" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
+      <c r="C3" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
     </row>
     <row r="4" spans="2:22" s="3" customFormat="1" ht="20" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
@@ -1954,220 +1889,218 @@
       <c r="U4" s="1"/>
     </row>
     <row r="5" spans="2:22" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.5">
-      <c r="C5" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
+      <c r="C5" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
     </row>
     <row r="6" spans="2:22" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.5">
-      <c r="C6" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
+      <c r="C6" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
     <row r="7" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="47"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-    </row>
-    <row r="9" spans="2:22" s="3" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
+    <row r="8" spans="2:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="29"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+    </row>
+    <row r="9" spans="2:22" s="3" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
     </row>
     <row r="10" spans="2:22" s="3" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="36" t="s">
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="U10" s="28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" s="3" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="U10" s="24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" s="3" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="31" t="s">
+      <c r="F11" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="I11" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="33" t="s">
+      <c r="N11" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="31" t="s">
+      <c r="O11" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="P11" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P11" s="31" t="s">
+      <c r="S11" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Q11" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="R11" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="S11" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="47" t="s">
-        <v>284</v>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="26" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="4" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="47"/>
+        <v>3</v>
+      </c>
+      <c r="D12" s="45"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="26"/>
     </row>
     <row r="13" spans="2:22" s="5" customFormat="1" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="2"/>
@@ -2186,19 +2119,19 @@
       <c r="S13" s="12"/>
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
-      <c r="V13" s="48">
+      <c r="V13" s="24">
         <v>184</v>
       </c>
     </row>
     <row r="14" spans="2:22" s="3" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="10"/>
@@ -2217,19 +2150,19 @@
       <c r="S14" s="12"/>
       <c r="T14" s="16"/>
       <c r="U14" s="17"/>
-      <c r="V14" s="49">
+      <c r="V14" s="25">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="10"/>
@@ -2248,19 +2181,19 @@
       <c r="S15" s="12"/>
       <c r="T15" s="16"/>
       <c r="U15" s="17"/>
-      <c r="V15" s="49">
+      <c r="V15" s="25">
         <v>207</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="10"/>
@@ -2279,19 +2212,19 @@
       <c r="S16" s="13"/>
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
-      <c r="V16" s="49">
+      <c r="V16" s="25">
         <v>176</v>
       </c>
     </row>
     <row r="17" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="10"/>
@@ -2310,19 +2243,19 @@
       <c r="S17" s="13"/>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
-      <c r="V17" s="49">
+      <c r="V17" s="25">
         <v>182</v>
       </c>
     </row>
     <row r="18" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="10"/>
@@ -2341,19 +2274,19 @@
       <c r="S18" s="13"/>
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
-      <c r="V18" s="49">
+      <c r="V18" s="25">
         <v>174</v>
       </c>
     </row>
     <row r="19" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="10"/>
@@ -2372,19 +2305,19 @@
       <c r="S19" s="13"/>
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
-      <c r="V19" s="49">
+      <c r="V19" s="25">
         <v>202</v>
       </c>
     </row>
     <row r="20" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="10"/>
@@ -2403,19 +2336,19 @@
       <c r="S20" s="13"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
-      <c r="V20" s="49">
+      <c r="V20" s="25">
         <v>207</v>
       </c>
     </row>
     <row r="21" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="10"/>
@@ -2434,19 +2367,19 @@
       <c r="S21" s="13"/>
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
-      <c r="V21" s="49">
+      <c r="V21" s="25">
         <v>207</v>
       </c>
     </row>
     <row r="22" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="10"/>
@@ -2465,19 +2398,19 @@
       <c r="S22" s="13"/>
       <c r="T22" s="17"/>
       <c r="U22" s="17"/>
-      <c r="V22" s="49">
+      <c r="V22" s="25">
         <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="10"/>
@@ -2496,19 +2429,19 @@
       <c r="S23" s="13"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
-      <c r="V23" s="49">
+      <c r="V23" s="25">
         <v>183</v>
       </c>
     </row>
     <row r="24" spans="2:22" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="10"/>
@@ -2527,19 +2460,19 @@
       <c r="S24" s="13"/>
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
-      <c r="V24" s="49">
+      <c r="V24" s="25">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="10"/>
@@ -2558,19 +2491,19 @@
       <c r="S25" s="13"/>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
-      <c r="V25" s="49">
+      <c r="V25" s="25">
         <v>200</v>
       </c>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="10"/>
@@ -2589,19 +2522,19 @@
       <c r="S26" s="13"/>
       <c r="T26" s="17"/>
       <c r="U26" s="17"/>
-      <c r="V26" s="49">
+      <c r="V26" s="25">
         <v>146</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="28" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="10"/>
@@ -2620,19 +2553,19 @@
       <c r="S27" s="13"/>
       <c r="T27" s="17"/>
       <c r="U27" s="17"/>
-      <c r="V27" s="49">
+      <c r="V27" s="25">
         <v>187</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B28" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="10"/>
@@ -2651,19 +2584,19 @@
       <c r="S28" s="13"/>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
-      <c r="V28" s="49">
+      <c r="V28" s="25">
         <v>183</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B29" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="10"/>
@@ -2682,19 +2615,19 @@
       <c r="S29" s="13"/>
       <c r="T29" s="17"/>
       <c r="U29" s="17"/>
-      <c r="V29" s="49">
+      <c r="V29" s="25">
         <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="10"/>
@@ -2713,19 +2646,19 @@
       <c r="S30" s="13"/>
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
-      <c r="V30" s="49">
+      <c r="V30" s="25">
         <v>158</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B31" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="10"/>
@@ -2744,19 +2677,19 @@
       <c r="S31" s="13"/>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
-      <c r="V31" s="49">
+      <c r="V31" s="25">
         <v>174</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B32" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="10"/>
@@ -2775,19 +2708,19 @@
       <c r="S32" s="13"/>
       <c r="T32" s="17"/>
       <c r="U32" s="17"/>
-      <c r="V32" s="49">
+      <c r="V32" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="10"/>
@@ -2806,19 +2739,19 @@
       <c r="S33" s="13"/>
       <c r="T33" s="17"/>
       <c r="U33" s="17"/>
-      <c r="V33" s="49">
+      <c r="V33" s="25">
         <v>145</v>
       </c>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="10"/>
@@ -2837,19 +2770,19 @@
       <c r="S34" s="13"/>
       <c r="T34" s="17"/>
       <c r="U34" s="17"/>
-      <c r="V34" s="49">
+      <c r="V34" s="25">
         <v>139</v>
       </c>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B35" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="10"/>
@@ -2868,19 +2801,19 @@
       <c r="S35" s="13"/>
       <c r="T35" s="17"/>
       <c r="U35" s="17"/>
-      <c r="V35" s="49">
+      <c r="V35" s="25">
         <v>173</v>
       </c>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B36" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="10"/>
@@ -2899,19 +2832,19 @@
       <c r="S36" s="13"/>
       <c r="T36" s="17"/>
       <c r="U36" s="17"/>
-      <c r="V36" s="49">
+      <c r="V36" s="25">
         <v>141</v>
       </c>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B37" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="10"/>
@@ -2930,19 +2863,19 @@
       <c r="S37" s="13"/>
       <c r="T37" s="17"/>
       <c r="U37" s="17"/>
-      <c r="V37" s="49">
+      <c r="V37" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B38" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="10"/>
@@ -2961,19 +2894,19 @@
       <c r="S38" s="13"/>
       <c r="T38" s="17"/>
       <c r="U38" s="17"/>
-      <c r="V38" s="49">
+      <c r="V38" s="25">
         <v>158</v>
       </c>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B39" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="10"/>
@@ -2992,19 +2925,19 @@
       <c r="S39" s="13"/>
       <c r="T39" s="17"/>
       <c r="U39" s="17"/>
-      <c r="V39" s="49">
+      <c r="V39" s="25">
         <v>152</v>
       </c>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B40" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="10"/>
@@ -3023,19 +2956,19 @@
       <c r="S40" s="13"/>
       <c r="T40" s="17"/>
       <c r="U40" s="17"/>
-      <c r="V40" s="49">
+      <c r="V40" s="25">
         <v>151</v>
       </c>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B41" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="10"/>
@@ -3054,19 +2987,19 @@
       <c r="S41" s="13"/>
       <c r="T41" s="17"/>
       <c r="U41" s="17"/>
-      <c r="V41" s="49">
+      <c r="V41" s="25">
         <v>163</v>
       </c>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B42" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="10"/>
@@ -3085,19 +3018,19 @@
       <c r="S42" s="13"/>
       <c r="T42" s="17"/>
       <c r="U42" s="17"/>
-      <c r="V42" s="49">
+      <c r="V42" s="25">
         <v>154</v>
       </c>
     </row>
     <row r="43" spans="2:22" ht="28" x14ac:dyDescent="0.35">
       <c r="B43" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="10"/>
@@ -3116,19 +3049,19 @@
       <c r="S43" s="13"/>
       <c r="T43" s="17"/>
       <c r="U43" s="17"/>
-      <c r="V43" s="49">
+      <c r="V43" s="25">
         <v>168</v>
       </c>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B44" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="10"/>
@@ -3147,19 +3080,19 @@
       <c r="S44" s="13"/>
       <c r="T44" s="17"/>
       <c r="U44" s="17"/>
-      <c r="V44" s="49">
+      <c r="V44" s="25">
         <v>161</v>
       </c>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B45" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="10"/>
@@ -3178,19 +3111,19 @@
       <c r="S45" s="13"/>
       <c r="T45" s="17"/>
       <c r="U45" s="17"/>
-      <c r="V45" s="49">
+      <c r="V45" s="25">
         <v>176</v>
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B46" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="10"/>
@@ -3209,19 +3142,19 @@
       <c r="S46" s="13"/>
       <c r="T46" s="17"/>
       <c r="U46" s="17"/>
-      <c r="V46" s="49">
+      <c r="V46" s="25">
         <v>149</v>
       </c>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B47" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="10"/>
@@ -3240,19 +3173,19 @@
       <c r="S47" s="13"/>
       <c r="T47" s="17"/>
       <c r="U47" s="17"/>
-      <c r="V47" s="49">
+      <c r="V47" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B48" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="10"/>
@@ -3271,19 +3204,19 @@
       <c r="S48" s="13"/>
       <c r="T48" s="17"/>
       <c r="U48" s="17"/>
-      <c r="V48" s="49">
+      <c r="V48" s="25">
         <v>167</v>
       </c>
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B49" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C49" s="18" t="s">
-        <v>233</v>
-      </c>
       <c r="D49" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="10"/>
@@ -3302,19 +3235,19 @@
       <c r="S49" s="13"/>
       <c r="T49" s="17"/>
       <c r="U49" s="17"/>
-      <c r="V49" s="49">
+      <c r="V49" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B50" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="10"/>
@@ -3333,19 +3266,19 @@
       <c r="S50" s="13"/>
       <c r="T50" s="17"/>
       <c r="U50" s="17"/>
-      <c r="V50" s="49">
+      <c r="V50" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="51" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B51" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="10"/>
@@ -3364,19 +3297,19 @@
       <c r="S51" s="13"/>
       <c r="T51" s="17"/>
       <c r="U51" s="17"/>
-      <c r="V51" s="49">
+      <c r="V51" s="25">
         <v>177</v>
       </c>
     </row>
     <row r="52" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B52" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="10"/>
@@ -3395,19 +3328,19 @@
       <c r="S52" s="13"/>
       <c r="T52" s="17"/>
       <c r="U52" s="17"/>
-      <c r="V52" s="49">
+      <c r="V52" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="53" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B53" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
@@ -3426,19 +3359,19 @@
       <c r="S53" s="13"/>
       <c r="T53" s="9"/>
       <c r="U53" s="9"/>
-      <c r="V53" s="49">
+      <c r="V53" s="25">
         <v>172</v>
       </c>
     </row>
     <row r="54" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B54" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
@@ -3457,19 +3390,19 @@
       <c r="S54" s="13"/>
       <c r="T54" s="9"/>
       <c r="U54" s="9"/>
-      <c r="V54" s="49">
+      <c r="V54" s="25">
         <v>200</v>
       </c>
     </row>
     <row r="55" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B55" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
@@ -3488,19 +3421,19 @@
       <c r="S55" s="13"/>
       <c r="T55" s="9"/>
       <c r="U55" s="9"/>
-      <c r="V55" s="49">
+      <c r="V55" s="25">
         <v>193</v>
       </c>
     </row>
     <row r="56" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B56" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
@@ -3519,19 +3452,19 @@
       <c r="S56" s="13"/>
       <c r="T56" s="9"/>
       <c r="U56" s="9"/>
-      <c r="V56" s="49">
+      <c r="V56" s="25">
         <v>200</v>
       </c>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B57" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
@@ -3550,19 +3483,19 @@
       <c r="S57" s="13"/>
       <c r="T57" s="9"/>
       <c r="U57" s="9"/>
-      <c r="V57" s="49">
+      <c r="V57" s="25">
         <v>203</v>
       </c>
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B58" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
@@ -3581,19 +3514,19 @@
       <c r="S58" s="13"/>
       <c r="T58" s="9"/>
       <c r="U58" s="9"/>
-      <c r="V58" s="49">
+      <c r="V58" s="25">
         <v>232</v>
       </c>
     </row>
     <row r="59" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B59" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
@@ -3612,19 +3545,19 @@
       <c r="S59" s="13"/>
       <c r="T59" s="9"/>
       <c r="U59" s="9"/>
-      <c r="V59" s="49">
+      <c r="V59" s="25">
         <v>207</v>
       </c>
     </row>
     <row r="60" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B60" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
@@ -3643,19 +3576,19 @@
       <c r="S60" s="13"/>
       <c r="T60" s="9"/>
       <c r="U60" s="9"/>
-      <c r="V60" s="49">
+      <c r="V60" s="25">
         <v>189</v>
       </c>
     </row>
     <row r="61" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B61" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
@@ -3674,19 +3607,19 @@
       <c r="S61" s="13"/>
       <c r="T61" s="9"/>
       <c r="U61" s="9"/>
-      <c r="V61" s="49">
+      <c r="V61" s="25">
         <v>170</v>
       </c>
     </row>
     <row r="62" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B62" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
@@ -3705,19 +3638,19 @@
       <c r="S62" s="13"/>
       <c r="T62" s="9"/>
       <c r="U62" s="9"/>
-      <c r="V62" s="49">
+      <c r="V62" s="25">
         <v>219</v>
       </c>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B63" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
@@ -3736,19 +3669,19 @@
       <c r="S63" s="13"/>
       <c r="T63" s="9"/>
       <c r="U63" s="9"/>
-      <c r="V63" s="49">
+      <c r="V63" s="25">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B64" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
@@ -3767,19 +3700,19 @@
       <c r="S64" s="13"/>
       <c r="T64" s="9"/>
       <c r="U64" s="9"/>
-      <c r="V64" s="49">
+      <c r="V64" s="25">
         <v>149</v>
       </c>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B65" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
@@ -3798,19 +3731,19 @@
       <c r="S65" s="13"/>
       <c r="T65" s="9"/>
       <c r="U65" s="9"/>
-      <c r="V65" s="49">
+      <c r="V65" s="25">
         <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:22" ht="28" x14ac:dyDescent="0.35">
       <c r="B66" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
@@ -3829,19 +3762,19 @@
       <c r="S66" s="13"/>
       <c r="T66" s="9"/>
       <c r="U66" s="9"/>
-      <c r="V66" s="49">
+      <c r="V66" s="25">
         <v>177</v>
       </c>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B67" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
@@ -3860,19 +3793,19 @@
       <c r="S67" s="13"/>
       <c r="T67" s="9"/>
       <c r="U67" s="9"/>
-      <c r="V67" s="49">
+      <c r="V67" s="25">
         <v>209</v>
       </c>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B68" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E68" s="9"/>
       <c r="F68" s="9"/>
@@ -3891,19 +3824,19 @@
       <c r="S68" s="13"/>
       <c r="T68" s="9"/>
       <c r="U68" s="9"/>
-      <c r="V68" s="49">
+      <c r="V68" s="25">
         <v>187</v>
       </c>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B69" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
@@ -3922,19 +3855,19 @@
       <c r="S69" s="13"/>
       <c r="T69" s="9"/>
       <c r="U69" s="9"/>
-      <c r="V69" s="49">
+      <c r="V69" s="25">
         <v>151</v>
       </c>
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B70" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
@@ -3953,19 +3886,19 @@
       <c r="S70" s="13"/>
       <c r="T70" s="9"/>
       <c r="U70" s="9"/>
-      <c r="V70" s="49">
+      <c r="V70" s="25">
         <v>166</v>
       </c>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B71" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
@@ -3984,19 +3917,19 @@
       <c r="S71" s="13"/>
       <c r="T71" s="9"/>
       <c r="U71" s="9"/>
-      <c r="V71" s="49">
+      <c r="V71" s="25">
         <v>204</v>
       </c>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B72" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
@@ -4015,19 +3948,19 @@
       <c r="S72" s="13"/>
       <c r="T72" s="9"/>
       <c r="U72" s="9"/>
-      <c r="V72" s="49">
+      <c r="V72" s="25">
         <v>194</v>
       </c>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B73" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C73" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="9" t="s">
-        <v>235</v>
-      </c>
       <c r="D73" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
@@ -4046,19 +3979,19 @@
       <c r="S73" s="13"/>
       <c r="T73" s="9"/>
       <c r="U73" s="9"/>
-      <c r="V73" s="49">
+      <c r="V73" s="25">
         <v>187</v>
       </c>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B74" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
@@ -4077,19 +4010,19 @@
       <c r="S74" s="13"/>
       <c r="T74" s="9"/>
       <c r="U74" s="9"/>
-      <c r="V74" s="49">
+      <c r="V74" s="25">
         <v>184</v>
       </c>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B75" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
@@ -4108,19 +4041,19 @@
       <c r="S75" s="13"/>
       <c r="T75" s="9"/>
       <c r="U75" s="9"/>
-      <c r="V75" s="49">
+      <c r="V75" s="25">
         <v>190</v>
       </c>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B76" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
@@ -4139,19 +4072,19 @@
       <c r="S76" s="13"/>
       <c r="T76" s="9"/>
       <c r="U76" s="9"/>
-      <c r="V76" s="49">
+      <c r="V76" s="25">
         <v>161</v>
       </c>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B77" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E77" s="9"/>
       <c r="F77" s="9"/>
@@ -4170,19 +4103,19 @@
       <c r="S77" s="13"/>
       <c r="T77" s="9"/>
       <c r="U77" s="9"/>
-      <c r="V77" s="49">
+      <c r="V77" s="25">
         <v>168</v>
       </c>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B78" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
@@ -4201,19 +4134,19 @@
       <c r="S78" s="13"/>
       <c r="T78" s="9"/>
       <c r="U78" s="9"/>
-      <c r="V78" s="49">
+      <c r="V78" s="25">
         <v>183</v>
       </c>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B79" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
@@ -4232,19 +4165,19 @@
       <c r="S79" s="13"/>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
-      <c r="V79" s="49">
+      <c r="V79" s="25">
         <v>173</v>
       </c>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B80" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
@@ -4263,19 +4196,19 @@
       <c r="S80" s="13"/>
       <c r="T80" s="9"/>
       <c r="U80" s="9"/>
-      <c r="V80" s="49">
+      <c r="V80" s="25">
         <v>200</v>
       </c>
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B81" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C81" s="21">
         <v>21</v>
       </c>
       <c r="D81" s="22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E81" s="9"/>
       <c r="F81" s="9"/>
@@ -4294,19 +4227,19 @@
       <c r="S81" s="13"/>
       <c r="T81" s="9"/>
       <c r="U81" s="9"/>
-      <c r="V81" s="49">
+      <c r="V81" s="25">
         <v>162</v>
       </c>
     </row>
     <row r="82" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B82" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9"/>
@@ -4325,7 +4258,7 @@
       <c r="S82" s="13"/>
       <c r="T82" s="9"/>
       <c r="U82" s="9"/>
-      <c r="V82" s="49">
+      <c r="V82" s="25">
         <v>145</v>
       </c>
     </row>
@@ -4337,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
@@ -4356,7 +4289,7 @@
       <c r="S83" s="13"/>
       <c r="T83" s="9"/>
       <c r="U83" s="9"/>
-      <c r="V83" s="49">
+      <c r="V83" s="25">
         <v>214</v>
       </c>
     </row>
@@ -4368,7 +4301,7 @@
         <v>2</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
@@ -4387,7 +4320,7 @@
       <c r="S84" s="13"/>
       <c r="T84" s="9"/>
       <c r="U84" s="9"/>
-      <c r="V84" s="49">
+      <c r="V84" s="25">
         <v>194</v>
       </c>
     </row>
@@ -4399,7 +4332,7 @@
         <v>3</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
@@ -4418,7 +4351,7 @@
       <c r="S85" s="13"/>
       <c r="T85" s="9"/>
       <c r="U85" s="9"/>
-      <c r="V85" s="49">
+      <c r="V85" s="25">
         <v>215</v>
       </c>
     </row>
@@ -4430,7 +4363,7 @@
         <v>4</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
@@ -4449,7 +4382,7 @@
       <c r="S86" s="13"/>
       <c r="T86" s="9"/>
       <c r="U86" s="9"/>
-      <c r="V86" s="49">
+      <c r="V86" s="25">
         <v>179</v>
       </c>
     </row>
@@ -4461,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
@@ -4480,7 +4413,7 @@
       <c r="S87" s="13"/>
       <c r="T87" s="9"/>
       <c r="U87" s="9"/>
-      <c r="V87" s="49">
+      <c r="V87" s="25">
         <v>153</v>
       </c>
     </row>
@@ -4492,7 +4425,7 @@
         <v>2</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
@@ -4511,7 +4444,7 @@
       <c r="S88" s="13"/>
       <c r="T88" s="9"/>
       <c r="U88" s="9"/>
-      <c r="V88" s="49">
+      <c r="V88" s="25">
         <v>175</v>
       </c>
     </row>
@@ -4523,7 +4456,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
@@ -4542,7 +4475,7 @@
       <c r="S89" s="13"/>
       <c r="T89" s="9"/>
       <c r="U89" s="9"/>
-      <c r="V89" s="49">
+      <c r="V89" s="25">
         <v>172</v>
       </c>
     </row>
@@ -4554,7 +4487,7 @@
         <v>4</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
@@ -4573,7 +4506,7 @@
       <c r="S90" s="13"/>
       <c r="T90" s="9"/>
       <c r="U90" s="9"/>
-      <c r="V90" s="49">
+      <c r="V90" s="25">
         <v>153</v>
       </c>
     </row>
@@ -4585,7 +4518,7 @@
         <v>5</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
@@ -4604,7 +4537,7 @@
       <c r="S91" s="13"/>
       <c r="T91" s="9"/>
       <c r="U91" s="9"/>
-      <c r="V91" s="49">
+      <c r="V91" s="25">
         <v>154</v>
       </c>
     </row>
@@ -4616,7 +4549,7 @@
         <v>6</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9"/>
@@ -4635,7 +4568,7 @@
       <c r="S92" s="13"/>
       <c r="T92" s="9"/>
       <c r="U92" s="9"/>
-      <c r="V92" s="49">
+      <c r="V92" s="25">
         <v>154</v>
       </c>
     </row>
@@ -4647,7 +4580,7 @@
         <v>7</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
@@ -4666,7 +4599,7 @@
       <c r="S93" s="13"/>
       <c r="T93" s="9"/>
       <c r="U93" s="9"/>
-      <c r="V93" s="49">
+      <c r="V93" s="25">
         <v>144</v>
       </c>
     </row>
@@ -4678,7 +4611,7 @@
         <v>8</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
@@ -4697,7 +4630,7 @@
       <c r="S94" s="13"/>
       <c r="T94" s="9"/>
       <c r="U94" s="9"/>
-      <c r="V94" s="49">
+      <c r="V94" s="25">
         <v>172</v>
       </c>
     </row>
@@ -4709,7 +4642,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
@@ -4728,7 +4661,7 @@
       <c r="S95" s="13"/>
       <c r="T95" s="9"/>
       <c r="U95" s="9"/>
-      <c r="V95" s="49">
+      <c r="V95" s="25">
         <v>153</v>
       </c>
     </row>
@@ -4740,7 +4673,7 @@
         <v>10</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
@@ -4759,7 +4692,7 @@
       <c r="S96" s="13"/>
       <c r="T96" s="9"/>
       <c r="U96" s="9"/>
-      <c r="V96" s="49">
+      <c r="V96" s="25">
         <v>197</v>
       </c>
     </row>
@@ -4771,7 +4704,7 @@
         <v>11</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
@@ -4790,7 +4723,7 @@
       <c r="S97" s="13"/>
       <c r="T97" s="9"/>
       <c r="U97" s="9"/>
-      <c r="V97" s="49">
+      <c r="V97" s="25">
         <v>163</v>
       </c>
     </row>
@@ -4802,7 +4735,7 @@
         <v>12</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
@@ -4821,7 +4754,7 @@
       <c r="S98" s="13"/>
       <c r="T98" s="9"/>
       <c r="U98" s="9"/>
-      <c r="V98" s="49">
+      <c r="V98" s="25">
         <v>173</v>
       </c>
     </row>
@@ -4833,7 +4766,7 @@
         <v>13</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
@@ -4852,7 +4785,7 @@
       <c r="S99" s="13"/>
       <c r="T99" s="9"/>
       <c r="U99" s="9"/>
-      <c r="V99" s="49">
+      <c r="V99" s="25">
         <v>188</v>
       </c>
     </row>
@@ -4864,7 +4797,7 @@
         <v>14</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9"/>
@@ -4883,7 +4816,7 @@
       <c r="S100" s="13"/>
       <c r="T100" s="9"/>
       <c r="U100" s="9"/>
-      <c r="V100" s="49">
+      <c r="V100" s="25">
         <v>176</v>
       </c>
     </row>
@@ -4895,7 +4828,7 @@
         <v>15</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
@@ -4914,7 +4847,7 @@
       <c r="S101" s="13"/>
       <c r="T101" s="9"/>
       <c r="U101" s="9"/>
-      <c r="V101" s="49">
+      <c r="V101" s="25">
         <v>153</v>
       </c>
     </row>
@@ -4926,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9"/>
@@ -4945,7 +4878,7 @@
       <c r="S102" s="13"/>
       <c r="T102" s="9"/>
       <c r="U102" s="9"/>
-      <c r="V102" s="49">
+      <c r="V102" s="25">
         <v>240</v>
       </c>
     </row>
@@ -4957,7 +4890,7 @@
         <v>2</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E103" s="9"/>
       <c r="F103" s="9"/>
@@ -4976,7 +4909,7 @@
       <c r="S103" s="13"/>
       <c r="T103" s="9"/>
       <c r="U103" s="9"/>
-      <c r="V103" s="49">
+      <c r="V103" s="25">
         <v>139</v>
       </c>
     </row>
@@ -4988,7 +4921,7 @@
         <v>3</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
@@ -5007,7 +4940,7 @@
       <c r="S104" s="13"/>
       <c r="T104" s="9"/>
       <c r="U104" s="9"/>
-      <c r="V104" s="49">
+      <c r="V104" s="25">
         <v>194</v>
       </c>
     </row>
@@ -5019,7 +4952,7 @@
         <v>4</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
@@ -5038,7 +4971,7 @@
       <c r="S105" s="13"/>
       <c r="T105" s="9"/>
       <c r="U105" s="9"/>
-      <c r="V105" s="49">
+      <c r="V105" s="25">
         <v>161</v>
       </c>
     </row>
@@ -5050,7 +4983,7 @@
         <v>5</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
@@ -5069,7 +5002,7 @@
       <c r="S106" s="13"/>
       <c r="T106" s="9"/>
       <c r="U106" s="9"/>
-      <c r="V106" s="49">
+      <c r="V106" s="25">
         <v>191</v>
       </c>
     </row>
@@ -5081,7 +5014,7 @@
         <v>6</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
@@ -5100,7 +5033,7 @@
       <c r="S107" s="13"/>
       <c r="T107" s="9"/>
       <c r="U107" s="9"/>
-      <c r="V107" s="49">
+      <c r="V107" s="25">
         <v>196</v>
       </c>
     </row>
@@ -5112,7 +5045,7 @@
         <v>7</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E108" s="9"/>
       <c r="F108" s="9"/>
@@ -5131,7 +5064,7 @@
       <c r="S108" s="13"/>
       <c r="T108" s="9"/>
       <c r="U108" s="9"/>
-      <c r="V108" s="49">
+      <c r="V108" s="25">
         <v>174</v>
       </c>
     </row>
@@ -5143,7 +5076,7 @@
         <v>8</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E109" s="9"/>
       <c r="F109" s="9"/>
@@ -5162,7 +5095,7 @@
       <c r="S109" s="13"/>
       <c r="T109" s="9"/>
       <c r="U109" s="9"/>
-      <c r="V109" s="49">
+      <c r="V109" s="25">
         <v>203</v>
       </c>
     </row>
@@ -5174,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
@@ -5193,7 +5126,7 @@
       <c r="S110" s="13"/>
       <c r="T110" s="9"/>
       <c r="U110" s="9"/>
-      <c r="V110" s="49">
+      <c r="V110" s="25">
         <v>195</v>
       </c>
     </row>
@@ -5205,7 +5138,7 @@
         <v>2</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
@@ -5224,7 +5157,7 @@
       <c r="S111" s="13"/>
       <c r="T111" s="9"/>
       <c r="U111" s="9"/>
-      <c r="V111" s="49">
+      <c r="V111" s="25">
         <v>211</v>
       </c>
     </row>
@@ -5236,7 +5169,7 @@
         <v>3</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E112" s="9"/>
       <c r="F112" s="9"/>
@@ -5255,7 +5188,7 @@
       <c r="S112" s="13"/>
       <c r="T112" s="9"/>
       <c r="U112" s="9"/>
-      <c r="V112" s="49">
+      <c r="V112" s="25">
         <v>193</v>
       </c>
     </row>
@@ -5267,7 +5200,7 @@
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E113" s="9"/>
       <c r="F113" s="9"/>
@@ -5286,7 +5219,7 @@
       <c r="S113" s="13"/>
       <c r="T113" s="9"/>
       <c r="U113" s="9"/>
-      <c r="V113" s="49">
+      <c r="V113" s="25">
         <v>168</v>
       </c>
     </row>
@@ -5298,7 +5231,7 @@
         <v>5</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E114" s="9"/>
       <c r="F114" s="9"/>
@@ -5317,7 +5250,7 @@
       <c r="S114" s="13"/>
       <c r="T114" s="9"/>
       <c r="U114" s="9"/>
-      <c r="V114" s="49">
+      <c r="V114" s="25">
         <v>180</v>
       </c>
     </row>
@@ -5329,7 +5262,7 @@
         <v>6</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
@@ -5348,7 +5281,7 @@
       <c r="S115" s="13"/>
       <c r="T115" s="9"/>
       <c r="U115" s="9"/>
-      <c r="V115" s="49">
+      <c r="V115" s="25">
         <v>180</v>
       </c>
     </row>
@@ -5360,7 +5293,7 @@
         <v>7</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
@@ -5379,7 +5312,7 @@
       <c r="S116" s="13"/>
       <c r="T116" s="9"/>
       <c r="U116" s="9"/>
-      <c r="V116" s="49">
+      <c r="V116" s="25">
         <v>175</v>
       </c>
     </row>
@@ -5391,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
@@ -5410,7 +5343,7 @@
       <c r="S117" s="13"/>
       <c r="T117" s="9"/>
       <c r="U117" s="9"/>
-      <c r="V117" s="49">
+      <c r="V117" s="25">
         <v>179</v>
       </c>
     </row>
@@ -5422,7 +5355,7 @@
         <v>2</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E118" s="9"/>
       <c r="F118" s="9"/>
@@ -5441,7 +5374,7 @@
       <c r="S118" s="13"/>
       <c r="T118" s="9"/>
       <c r="U118" s="9"/>
-      <c r="V118" s="49">
+      <c r="V118" s="25">
         <v>163</v>
       </c>
     </row>
@@ -5453,7 +5386,7 @@
         <v>3</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
@@ -5472,7 +5405,7 @@
       <c r="S119" s="13"/>
       <c r="T119" s="9"/>
       <c r="U119" s="9"/>
-      <c r="V119" s="49">
+      <c r="V119" s="25">
         <v>183</v>
       </c>
     </row>
@@ -5484,7 +5417,7 @@
         <v>4</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E120" s="9"/>
       <c r="F120" s="9"/>
@@ -5503,7 +5436,7 @@
       <c r="S120" s="13"/>
       <c r="T120" s="9"/>
       <c r="U120" s="9"/>
-      <c r="V120" s="49">
+      <c r="V120" s="25">
         <v>169</v>
       </c>
     </row>
@@ -5515,7 +5448,7 @@
         <v>5</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E121" s="9"/>
       <c r="F121" s="9"/>
@@ -5534,7 +5467,7 @@
       <c r="S121" s="13"/>
       <c r="T121" s="9"/>
       <c r="U121" s="9"/>
-      <c r="V121" s="49">
+      <c r="V121" s="25">
         <v>172</v>
       </c>
     </row>
@@ -5546,7 +5479,7 @@
         <v>6</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E122" s="9"/>
       <c r="F122" s="9"/>
@@ -5565,7 +5498,7 @@
       <c r="S122" s="13"/>
       <c r="T122" s="9"/>
       <c r="U122" s="9"/>
-      <c r="V122" s="49">
+      <c r="V122" s="25">
         <v>155</v>
       </c>
     </row>
@@ -5577,7 +5510,7 @@
         <v>7</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
@@ -5596,7 +5529,7 @@
       <c r="S123" s="13"/>
       <c r="T123" s="9"/>
       <c r="U123" s="9"/>
-      <c r="V123" s="49">
+      <c r="V123" s="25">
         <v>135</v>
       </c>
     </row>
@@ -5608,7 +5541,7 @@
         <v>8</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E124" s="9"/>
       <c r="F124" s="9"/>
@@ -5627,7 +5560,7 @@
       <c r="S124" s="13"/>
       <c r="T124" s="9"/>
       <c r="U124" s="9"/>
-      <c r="V124" s="49">
+      <c r="V124" s="25">
         <v>208</v>
       </c>
     </row>
@@ -5639,7 +5572,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E125" s="9"/>
       <c r="F125" s="9"/>
@@ -5658,7 +5591,7 @@
       <c r="S125" s="13"/>
       <c r="T125" s="9"/>
       <c r="U125" s="9"/>
-      <c r="V125" s="49">
+      <c r="V125" s="25">
         <v>175</v>
       </c>
     </row>
@@ -5670,7 +5603,7 @@
         <v>10</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E126" s="9"/>
       <c r="F126" s="9"/>
@@ -5689,7 +5622,7 @@
       <c r="S126" s="13"/>
       <c r="T126" s="9"/>
       <c r="U126" s="9"/>
-      <c r="V126" s="49">
+      <c r="V126" s="25">
         <v>170</v>
       </c>
     </row>
@@ -5701,7 +5634,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9"/>
@@ -5720,7 +5653,7 @@
       <c r="S127" s="13"/>
       <c r="T127" s="9"/>
       <c r="U127" s="9"/>
-      <c r="V127" s="49">
+      <c r="V127" s="25">
         <v>196</v>
       </c>
     </row>
@@ -5732,7 +5665,7 @@
         <v>12</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E128" s="9"/>
       <c r="F128" s="9"/>
@@ -5751,7 +5684,7 @@
       <c r="S128" s="13"/>
       <c r="T128" s="9"/>
       <c r="U128" s="9"/>
-      <c r="V128" s="49">
+      <c r="V128" s="25">
         <v>159</v>
       </c>
     </row>
@@ -5763,7 +5696,7 @@
         <v>13</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
@@ -5782,7 +5715,7 @@
       <c r="S129" s="13"/>
       <c r="T129" s="9"/>
       <c r="U129" s="9"/>
-      <c r="V129" s="49">
+      <c r="V129" s="25">
         <v>153</v>
       </c>
     </row>
@@ -5794,7 +5727,7 @@
         <v>14</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
@@ -5813,7 +5746,7 @@
       <c r="S130" s="13"/>
       <c r="T130" s="9"/>
       <c r="U130" s="9"/>
-      <c r="V130" s="49">
+      <c r="V130" s="25">
         <v>131</v>
       </c>
     </row>
@@ -5825,7 +5758,7 @@
         <v>15</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
@@ -5844,7 +5777,7 @@
       <c r="S131" s="13"/>
       <c r="T131" s="9"/>
       <c r="U131" s="9"/>
-      <c r="V131" s="49">
+      <c r="V131" s="25">
         <v>181</v>
       </c>
     </row>
@@ -5856,7 +5789,7 @@
         <v>16</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E132" s="9"/>
       <c r="F132" s="9"/>
@@ -5875,7 +5808,7 @@
       <c r="S132" s="13"/>
       <c r="T132" s="9"/>
       <c r="U132" s="9"/>
-      <c r="V132" s="49">
+      <c r="V132" s="25">
         <v>153</v>
       </c>
     </row>
@@ -5887,7 +5820,7 @@
         <v>17</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E133" s="9"/>
       <c r="F133" s="9"/>
@@ -5906,7 +5839,7 @@
       <c r="S133" s="13"/>
       <c r="T133" s="9"/>
       <c r="U133" s="9"/>
-      <c r="V133" s="49">
+      <c r="V133" s="25">
         <v>161</v>
       </c>
     </row>
@@ -5918,7 +5851,7 @@
         <v>18</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E134" s="9"/>
       <c r="F134" s="9"/>
@@ -5937,7 +5870,7 @@
       <c r="S134" s="13"/>
       <c r="T134" s="9"/>
       <c r="U134" s="9"/>
-      <c r="V134" s="49">
+      <c r="V134" s="25">
         <v>186</v>
       </c>
     </row>
@@ -5949,7 +5882,7 @@
         <v>19</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E135" s="9"/>
       <c r="F135" s="9"/>
@@ -5968,7 +5901,7 @@
       <c r="S135" s="13"/>
       <c r="T135" s="9"/>
       <c r="U135" s="9"/>
-      <c r="V135" s="49">
+      <c r="V135" s="25">
         <v>193</v>
       </c>
     </row>
@@ -5980,7 +5913,7 @@
         <v>20</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E136" s="9"/>
       <c r="F136" s="9"/>
@@ -5999,7 +5932,7 @@
       <c r="S136" s="13"/>
       <c r="T136" s="9"/>
       <c r="U136" s="9"/>
-      <c r="V136" s="49">
+      <c r="V136" s="25">
         <v>138</v>
       </c>
     </row>
@@ -6011,7 +5944,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E137" s="9"/>
       <c r="F137" s="9"/>
@@ -6030,7 +5963,7 @@
       <c r="S137" s="13"/>
       <c r="T137" s="9"/>
       <c r="U137" s="9"/>
-      <c r="V137" s="49">
+      <c r="V137" s="25">
         <v>179</v>
       </c>
     </row>
@@ -6042,7 +5975,7 @@
         <v>2</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E138" s="9"/>
       <c r="F138" s="9"/>
@@ -6061,7 +5994,7 @@
       <c r="S138" s="13"/>
       <c r="T138" s="9"/>
       <c r="U138" s="9"/>
-      <c r="V138" s="49">
+      <c r="V138" s="25">
         <v>135</v>
       </c>
     </row>
@@ -6073,7 +6006,7 @@
         <v>3</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E139" s="9"/>
       <c r="F139" s="9"/>
@@ -6092,7 +6025,7 @@
       <c r="S139" s="13"/>
       <c r="T139" s="9"/>
       <c r="U139" s="9"/>
-      <c r="V139" s="49">
+      <c r="V139" s="25">
         <v>160</v>
       </c>
     </row>
@@ -6104,7 +6037,7 @@
         <v>4</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E140" s="9"/>
       <c r="F140" s="9"/>
@@ -6123,7 +6056,7 @@
       <c r="S140" s="13"/>
       <c r="T140" s="9"/>
       <c r="U140" s="9"/>
-      <c r="V140" s="49">
+      <c r="V140" s="25">
         <v>145</v>
       </c>
     </row>
@@ -6135,7 +6068,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E141" s="9"/>
       <c r="F141" s="9"/>
@@ -6154,7 +6087,7 @@
       <c r="S141" s="13"/>
       <c r="T141" s="9"/>
       <c r="U141" s="9"/>
-      <c r="V141" s="49">
+      <c r="V141" s="25">
         <v>141</v>
       </c>
     </row>
@@ -6166,7 +6099,7 @@
         <v>6</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E142" s="9"/>
       <c r="F142" s="9"/>
@@ -6185,7 +6118,7 @@
       <c r="S142" s="13"/>
       <c r="T142" s="9"/>
       <c r="U142" s="9"/>
-      <c r="V142" s="49">
+      <c r="V142" s="25">
         <v>163</v>
       </c>
     </row>
@@ -6197,7 +6130,7 @@
         <v>7</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E143" s="9"/>
       <c r="F143" s="9"/>
@@ -6216,7 +6149,7 @@
       <c r="S143" s="13"/>
       <c r="T143" s="9"/>
       <c r="U143" s="9"/>
-      <c r="V143" s="49">
+      <c r="V143" s="25">
         <v>172</v>
       </c>
     </row>
@@ -6228,7 +6161,7 @@
         <v>8</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
@@ -6247,7 +6180,7 @@
       <c r="S144" s="13"/>
       <c r="T144" s="9"/>
       <c r="U144" s="9"/>
-      <c r="V144" s="49">
+      <c r="V144" s="25">
         <v>163</v>
       </c>
     </row>
@@ -6259,7 +6192,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E145" s="9"/>
       <c r="F145" s="9"/>
@@ -6278,7 +6211,7 @@
       <c r="S145" s="13"/>
       <c r="T145" s="9"/>
       <c r="U145" s="9"/>
-      <c r="V145" s="49">
+      <c r="V145" s="25">
         <v>166</v>
       </c>
     </row>
@@ -6290,7 +6223,7 @@
         <v>10</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E146" s="9"/>
       <c r="F146" s="9"/>
@@ -6309,7 +6242,7 @@
       <c r="S146" s="13"/>
       <c r="T146" s="9"/>
       <c r="U146" s="9"/>
-      <c r="V146" s="49">
+      <c r="V146" s="25">
         <v>142</v>
       </c>
     </row>
@@ -6321,7 +6254,7 @@
         <v>11</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
@@ -6340,7 +6273,7 @@
       <c r="S147" s="13"/>
       <c r="T147" s="9"/>
       <c r="U147" s="9"/>
-      <c r="V147" s="49">
+      <c r="V147" s="25">
         <v>156</v>
       </c>
     </row>
@@ -6352,7 +6285,7 @@
         <v>12</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E148" s="9"/>
       <c r="F148" s="9"/>
@@ -6371,7 +6304,7 @@
       <c r="S148" s="13"/>
       <c r="T148" s="9"/>
       <c r="U148" s="9"/>
-      <c r="V148" s="49">
+      <c r="V148" s="25">
         <v>140</v>
       </c>
     </row>
@@ -6383,7 +6316,7 @@
         <v>13</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E149" s="9"/>
       <c r="F149" s="9"/>
@@ -6402,7 +6335,7 @@
       <c r="S149" s="13"/>
       <c r="T149" s="9"/>
       <c r="U149" s="9"/>
-      <c r="V149" s="49">
+      <c r="V149" s="25">
         <v>187</v>
       </c>
     </row>
@@ -6414,7 +6347,7 @@
         <v>14</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E150" s="9"/>
       <c r="F150" s="9"/>
@@ -6433,7 +6366,7 @@
       <c r="S150" s="13"/>
       <c r="T150" s="9"/>
       <c r="U150" s="9"/>
-      <c r="V150" s="49">
+      <c r="V150" s="25">
         <v>134</v>
       </c>
     </row>
@@ -6445,7 +6378,7 @@
         <v>15</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
@@ -6464,7 +6397,7 @@
       <c r="S151" s="13"/>
       <c r="T151" s="9"/>
       <c r="U151" s="9"/>
-      <c r="V151" s="49">
+      <c r="V151" s="25">
         <v>165</v>
       </c>
     </row>
@@ -6476,7 +6409,7 @@
         <v>16</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E152" s="9"/>
       <c r="F152" s="9"/>
@@ -6495,7 +6428,7 @@
       <c r="S152" s="13"/>
       <c r="T152" s="9"/>
       <c r="U152" s="9"/>
-      <c r="V152" s="49">
+      <c r="V152" s="25">
         <v>151</v>
       </c>
     </row>
@@ -6507,7 +6440,7 @@
         <v>17</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E153" s="9"/>
       <c r="F153" s="9"/>
@@ -6526,7 +6459,7 @@
       <c r="S153" s="13"/>
       <c r="T153" s="9"/>
       <c r="U153" s="9"/>
-      <c r="V153" s="49">
+      <c r="V153" s="25">
         <v>135</v>
       </c>
     </row>
@@ -6538,7 +6471,7 @@
         <v>18</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E154" s="9"/>
       <c r="F154" s="9"/>
@@ -6557,7 +6490,7 @@
       <c r="S154" s="13"/>
       <c r="T154" s="9"/>
       <c r="U154" s="9"/>
-      <c r="V154" s="49">
+      <c r="V154" s="25">
         <v>170</v>
       </c>
     </row>
@@ -6569,7 +6502,7 @@
         <v>19</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
@@ -6588,7 +6521,7 @@
       <c r="S155" s="13"/>
       <c r="T155" s="9"/>
       <c r="U155" s="9"/>
-      <c r="V155" s="49">
+      <c r="V155" s="25">
         <v>203</v>
       </c>
     </row>
@@ -6600,7 +6533,7 @@
         <v>20</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E156" s="9"/>
       <c r="F156" s="9"/>
@@ -6619,7 +6552,7 @@
       <c r="S156" s="13"/>
       <c r="T156" s="9"/>
       <c r="U156" s="9"/>
-      <c r="V156" s="49">
+      <c r="V156" s="25">
         <v>124</v>
       </c>
     </row>
@@ -6631,7 +6564,7 @@
         <v>21</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E157" s="9"/>
       <c r="F157" s="9"/>
@@ -6650,7 +6583,7 @@
       <c r="S157" s="13"/>
       <c r="T157" s="9"/>
       <c r="U157" s="9"/>
-      <c r="V157" s="49">
+      <c r="V157" s="25">
         <v>152</v>
       </c>
     </row>
@@ -6662,7 +6595,7 @@
         <v>22</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E158" s="9"/>
       <c r="F158" s="9"/>
@@ -6681,7 +6614,7 @@
       <c r="S158" s="13"/>
       <c r="T158" s="9"/>
       <c r="U158" s="9"/>
-      <c r="V158" s="49">
+      <c r="V158" s="25">
         <v>177</v>
       </c>
     </row>
@@ -6693,7 +6626,7 @@
         <v>23</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E159" s="9"/>
       <c r="F159" s="9"/>
@@ -6712,7 +6645,7 @@
       <c r="S159" s="13"/>
       <c r="T159" s="9"/>
       <c r="U159" s="9"/>
-      <c r="V159" s="49">
+      <c r="V159" s="25">
         <v>154</v>
       </c>
     </row>
@@ -6724,7 +6657,7 @@
         <v>24</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E160" s="9"/>
       <c r="F160" s="9"/>
@@ -6743,7 +6676,7 @@
       <c r="S160" s="13"/>
       <c r="T160" s="9"/>
       <c r="U160" s="9"/>
-      <c r="V160" s="49">
+      <c r="V160" s="25">
         <v>201</v>
       </c>
     </row>
@@ -6755,7 +6688,7 @@
         <v>25</v>
       </c>
       <c r="D161" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E161" s="9"/>
       <c r="F161" s="9"/>
@@ -6774,7 +6707,7 @@
       <c r="S161" s="13"/>
       <c r="T161" s="9"/>
       <c r="U161" s="9"/>
-      <c r="V161" s="49">
+      <c r="V161" s="25">
         <v>138</v>
       </c>
     </row>
@@ -6786,7 +6719,7 @@
         <v>26</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E162" s="9"/>
       <c r="F162" s="9"/>
@@ -6805,7 +6738,7 @@
       <c r="S162" s="13"/>
       <c r="T162" s="9"/>
       <c r="U162" s="9"/>
-      <c r="V162" s="49">
+      <c r="V162" s="25">
         <v>160</v>
       </c>
     </row>
@@ -6817,7 +6750,7 @@
         <v>27</v>
       </c>
       <c r="D163" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E163" s="9"/>
       <c r="F163" s="9"/>
@@ -6836,7 +6769,7 @@
       <c r="S163" s="13"/>
       <c r="T163" s="9"/>
       <c r="U163" s="9"/>
-      <c r="V163" s="49">
+      <c r="V163" s="25">
         <v>172</v>
       </c>
     </row>
@@ -6848,7 +6781,7 @@
         <v>28</v>
       </c>
       <c r="D164" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
@@ -6867,7 +6800,7 @@
       <c r="S164" s="13"/>
       <c r="T164" s="9"/>
       <c r="U164" s="9"/>
-      <c r="V164" s="49">
+      <c r="V164" s="25">
         <v>151</v>
       </c>
     </row>
@@ -6879,7 +6812,7 @@
         <v>29</v>
       </c>
       <c r="D165" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
@@ -6898,7 +6831,7 @@
       <c r="S165" s="13"/>
       <c r="T165" s="9"/>
       <c r="U165" s="9"/>
-      <c r="V165" s="49">
+      <c r="V165" s="25">
         <v>182</v>
       </c>
     </row>
@@ -6910,7 +6843,7 @@
         <v>30</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E166" s="9"/>
       <c r="F166" s="9"/>
@@ -6929,7 +6862,7 @@
       <c r="S166" s="13"/>
       <c r="T166" s="9"/>
       <c r="U166" s="9"/>
-      <c r="V166" s="49">
+      <c r="V166" s="25">
         <v>137</v>
       </c>
     </row>
@@ -6941,7 +6874,7 @@
         <v>31</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E167" s="9"/>
       <c r="F167" s="9"/>
@@ -6960,7 +6893,7 @@
       <c r="S167" s="13"/>
       <c r="T167" s="9"/>
       <c r="U167" s="9"/>
-      <c r="V167" s="49">
+      <c r="V167" s="25">
         <v>184</v>
       </c>
     </row>
@@ -6972,7 +6905,7 @@
         <v>32</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E168" s="9"/>
       <c r="F168" s="9"/>
@@ -6991,7 +6924,7 @@
       <c r="S168" s="13"/>
       <c r="T168" s="9"/>
       <c r="U168" s="9"/>
-      <c r="V168" s="49">
+      <c r="V168" s="25">
         <v>132</v>
       </c>
     </row>
@@ -7003,7 +6936,7 @@
         <v>33</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E169" s="9"/>
       <c r="F169" s="9"/>
@@ -7022,7 +6955,7 @@
       <c r="S169" s="13"/>
       <c r="T169" s="9"/>
       <c r="U169" s="9"/>
-      <c r="V169" s="49">
+      <c r="V169" s="25">
         <v>151</v>
       </c>
     </row>
@@ -7034,7 +6967,7 @@
         <v>34</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E170" s="9"/>
       <c r="F170" s="9"/>
@@ -7053,7 +6986,7 @@
       <c r="S170" s="13"/>
       <c r="T170" s="9"/>
       <c r="U170" s="9"/>
-      <c r="V170" s="49">
+      <c r="V170" s="25">
         <v>181</v>
       </c>
     </row>
@@ -7065,7 +6998,7 @@
         <v>35</v>
       </c>
       <c r="D171" s="13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
@@ -7084,7 +7017,7 @@
       <c r="S171" s="13"/>
       <c r="T171" s="9"/>
       <c r="U171" s="9"/>
-      <c r="V171" s="49">
+      <c r="V171" s="25">
         <v>174</v>
       </c>
     </row>
@@ -7096,7 +7029,7 @@
         <v>36</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
@@ -7115,7 +7048,7 @@
       <c r="S172" s="13"/>
       <c r="T172" s="9"/>
       <c r="U172" s="9"/>
-      <c r="V172" s="49">
+      <c r="V172" s="25">
         <v>183</v>
       </c>
     </row>
@@ -7127,7 +7060,7 @@
         <v>37</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E173" s="9"/>
       <c r="F173" s="9"/>
@@ -7146,7 +7079,7 @@
       <c r="S173" s="13"/>
       <c r="T173" s="9"/>
       <c r="U173" s="9"/>
-      <c r="V173" s="49">
+      <c r="V173" s="25">
         <v>166</v>
       </c>
     </row>
@@ -7158,7 +7091,7 @@
         <v>38</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E174" s="9"/>
       <c r="F174" s="9"/>
@@ -7177,7 +7110,7 @@
       <c r="S174" s="13"/>
       <c r="T174" s="9"/>
       <c r="U174" s="9"/>
-      <c r="V174" s="49">
+      <c r="V174" s="25">
         <v>140</v>
       </c>
     </row>
@@ -7189,7 +7122,7 @@
         <v>39</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
@@ -7208,7 +7141,7 @@
       <c r="S175" s="13"/>
       <c r="T175" s="9"/>
       <c r="U175" s="9"/>
-      <c r="V175" s="49">
+      <c r="V175" s="25">
         <v>137</v>
       </c>
     </row>
@@ -7220,7 +7153,7 @@
         <v>40</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
@@ -7239,7 +7172,7 @@
       <c r="S176" s="13"/>
       <c r="T176" s="9"/>
       <c r="U176" s="9"/>
-      <c r="V176" s="49">
+      <c r="V176" s="25">
         <v>175</v>
       </c>
     </row>
@@ -7248,10 +7181,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E177" s="9"/>
       <c r="F177" s="9"/>
@@ -7270,7 +7203,7 @@
       <c r="S177" s="13"/>
       <c r="T177" s="9"/>
       <c r="U177" s="9"/>
-      <c r="V177" s="49">
+      <c r="V177" s="25">
         <v>160</v>
       </c>
     </row>
@@ -7279,10 +7212,10 @@
         <v>16</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
@@ -7301,7 +7234,7 @@
       <c r="S178" s="13"/>
       <c r="T178" s="9"/>
       <c r="U178" s="9"/>
-      <c r="V178" s="49">
+      <c r="V178" s="25">
         <v>166</v>
       </c>
     </row>
@@ -7310,10 +7243,10 @@
         <v>16</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D179" s="13" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
@@ -7332,7 +7265,7 @@
       <c r="S179" s="13"/>
       <c r="T179" s="9"/>
       <c r="U179" s="9"/>
-      <c r="V179" s="49">
+      <c r="V179" s="25">
         <v>187</v>
       </c>
     </row>
@@ -7341,10 +7274,10 @@
         <v>16</v>
       </c>
       <c r="C180" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D180" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
@@ -7363,7 +7296,7 @@
       <c r="S180" s="13"/>
       <c r="T180" s="9"/>
       <c r="U180" s="9"/>
-      <c r="V180" s="49">
+      <c r="V180" s="25">
         <v>181</v>
       </c>
     </row>
@@ -7372,10 +7305,10 @@
         <v>16</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D181" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E181" s="9"/>
       <c r="F181" s="9"/>
@@ -7394,7 +7327,7 @@
       <c r="S181" s="13"/>
       <c r="T181" s="9"/>
       <c r="U181" s="9"/>
-      <c r="V181" s="49">
+      <c r="V181" s="25">
         <v>195</v>
       </c>
     </row>
@@ -7403,10 +7336,10 @@
         <v>16</v>
       </c>
       <c r="C182" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D182" s="13" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E182" s="9"/>
       <c r="F182" s="9"/>
@@ -7425,7 +7358,7 @@
       <c r="S182" s="13"/>
       <c r="T182" s="9"/>
       <c r="U182" s="9"/>
-      <c r="V182" s="49">
+      <c r="V182" s="25">
         <v>188</v>
       </c>
     </row>
@@ -7434,10 +7367,10 @@
         <v>16</v>
       </c>
       <c r="C183" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D183" s="13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
@@ -7456,7 +7389,7 @@
       <c r="S183" s="13"/>
       <c r="T183" s="9"/>
       <c r="U183" s="9"/>
-      <c r="V183" s="49">
+      <c r="V183" s="25">
         <v>214</v>
       </c>
     </row>
@@ -7465,10 +7398,10 @@
         <v>16</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D184" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
@@ -7487,7 +7420,7 @@
       <c r="S184" s="13"/>
       <c r="T184" s="9"/>
       <c r="U184" s="9"/>
-      <c r="V184" s="49">
+      <c r="V184" s="25">
         <v>170</v>
       </c>
     </row>
@@ -7496,10 +7429,10 @@
         <v>16</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D185" s="13" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
@@ -7518,7 +7451,7 @@
       <c r="S185" s="13"/>
       <c r="T185" s="9"/>
       <c r="U185" s="9"/>
-      <c r="V185" s="49">
+      <c r="V185" s="25">
         <v>161</v>
       </c>
     </row>
@@ -7527,10 +7460,10 @@
         <v>16</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D186" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
@@ -7549,7 +7482,7 @@
       <c r="S186" s="13"/>
       <c r="T186" s="9"/>
       <c r="U186" s="9"/>
-      <c r="V186" s="49">
+      <c r="V186" s="25">
         <v>183</v>
       </c>
     </row>
@@ -7558,10 +7491,10 @@
         <v>16</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D187" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
@@ -7580,7 +7513,7 @@
       <c r="S187" s="13"/>
       <c r="T187" s="9"/>
       <c r="U187" s="9"/>
-      <c r="V187" s="49">
+      <c r="V187" s="25">
         <v>173</v>
       </c>
     </row>
@@ -7589,10 +7522,10 @@
         <v>17</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D188" s="13" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E188" s="9"/>
       <c r="F188" s="9"/>
@@ -7611,7 +7544,7 @@
       <c r="S188" s="13"/>
       <c r="T188" s="9"/>
       <c r="U188" s="9"/>
-      <c r="V188" s="49">
+      <c r="V188" s="25">
         <v>163</v>
       </c>
     </row>
@@ -7620,10 +7553,10 @@
         <v>17</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D189" s="13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
@@ -7642,7 +7575,7 @@
       <c r="S189" s="13"/>
       <c r="T189" s="9"/>
       <c r="U189" s="9"/>
-      <c r="V189" s="49">
+      <c r="V189" s="25">
         <v>162</v>
       </c>
     </row>
@@ -7651,10 +7584,10 @@
         <v>17</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D190" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E190" s="9"/>
       <c r="F190" s="9"/>
@@ -7673,7 +7606,7 @@
       <c r="S190" s="13"/>
       <c r="T190" s="9"/>
       <c r="U190" s="9"/>
-      <c r="V190" s="49">
+      <c r="V190" s="25">
         <v>153</v>
       </c>
     </row>
@@ -7682,10 +7615,10 @@
         <v>17</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D191" s="13" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
@@ -7704,7 +7637,7 @@
       <c r="S191" s="13"/>
       <c r="T191" s="9"/>
       <c r="U191" s="9"/>
-      <c r="V191" s="49">
+      <c r="V191" s="25">
         <v>160</v>
       </c>
     </row>
@@ -7713,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D192" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E192" s="9"/>
       <c r="F192" s="9"/>
@@ -7735,7 +7668,7 @@
       <c r="S192" s="13"/>
       <c r="T192" s="9"/>
       <c r="U192" s="9"/>
-      <c r="V192" s="49">
+      <c r="V192" s="25">
         <v>134</v>
       </c>
     </row>
@@ -7747,7 +7680,7 @@
         <v>1</v>
       </c>
       <c r="D193" s="13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
@@ -7766,7 +7699,7 @@
       <c r="S193" s="13"/>
       <c r="T193" s="9"/>
       <c r="U193" s="9"/>
-      <c r="V193" s="49">
+      <c r="V193" s="25">
         <v>174</v>
       </c>
     </row>
@@ -7778,7 +7711,7 @@
         <v>2</v>
       </c>
       <c r="D194" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E194" s="9"/>
       <c r="F194" s="9"/>
@@ -7797,7 +7730,7 @@
       <c r="S194" s="13"/>
       <c r="T194" s="9"/>
       <c r="U194" s="9"/>
-      <c r="V194" s="49">
+      <c r="V194" s="25">
         <v>181</v>
       </c>
     </row>
@@ -7809,7 +7742,7 @@
         <v>3</v>
       </c>
       <c r="D195" s="13" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
@@ -7828,7 +7761,7 @@
       <c r="S195" s="13"/>
       <c r="T195" s="9"/>
       <c r="U195" s="9"/>
-      <c r="V195" s="49">
+      <c r="V195" s="25">
         <v>195</v>
       </c>
     </row>
@@ -7837,10 +7770,10 @@
         <v>19</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D196" s="13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E196" s="9"/>
       <c r="F196" s="9"/>
@@ -7859,7 +7792,7 @@
       <c r="S196" s="13"/>
       <c r="T196" s="9"/>
       <c r="U196" s="9"/>
-      <c r="V196" s="49">
+      <c r="V196" s="25">
         <v>163</v>
       </c>
     </row>
@@ -7868,10 +7801,10 @@
         <v>19</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D197" s="13" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
@@ -7890,7 +7823,7 @@
       <c r="S197" s="13"/>
       <c r="T197" s="9"/>
       <c r="U197" s="9"/>
-      <c r="V197" s="49">
+      <c r="V197" s="25">
         <v>177</v>
       </c>
     </row>
@@ -7899,10 +7832,10 @@
         <v>19</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D198" s="13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
@@ -7921,7 +7854,7 @@
       <c r="S198" s="13"/>
       <c r="T198" s="9"/>
       <c r="U198" s="9"/>
-      <c r="V198" s="49">
+      <c r="V198" s="25">
         <v>163</v>
       </c>
     </row>
@@ -7930,10 +7863,10 @@
         <v>19</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D199" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
@@ -7952,7 +7885,7 @@
       <c r="S199" s="13"/>
       <c r="T199" s="9"/>
       <c r="U199" s="9"/>
-      <c r="V199" s="49">
+      <c r="V199" s="25">
         <v>172</v>
       </c>
     </row>
@@ -7961,10 +7894,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D200" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E200" s="9"/>
       <c r="F200" s="9"/>
@@ -7983,7 +7916,7 @@
       <c r="S200" s="13"/>
       <c r="T200" s="9"/>
       <c r="U200" s="9"/>
-      <c r="V200" s="49">
+      <c r="V200" s="25">
         <v>149</v>
       </c>
     </row>
@@ -7992,10 +7925,10 @@
         <v>19</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D201" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E201" s="9"/>
       <c r="F201" s="9"/>
@@ -8014,7 +7947,7 @@
       <c r="S201" s="13"/>
       <c r="T201" s="9"/>
       <c r="U201" s="9"/>
-      <c r="V201" s="49">
+      <c r="V201" s="25">
         <v>163</v>
       </c>
     </row>
@@ -8023,10 +7956,10 @@
         <v>19</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D202" s="13" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E202" s="9"/>
       <c r="F202" s="9"/>
@@ -8045,7 +7978,7 @@
       <c r="S202" s="13"/>
       <c r="T202" s="9"/>
       <c r="U202" s="9"/>
-      <c r="V202" s="49">
+      <c r="V202" s="25">
         <v>141</v>
       </c>
     </row>
@@ -8054,10 +7987,10 @@
         <v>19</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D203" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E203" s="9"/>
       <c r="F203" s="9"/>
@@ -8076,7 +8009,7 @@
       <c r="S203" s="13"/>
       <c r="T203" s="9"/>
       <c r="U203" s="9"/>
-      <c r="V203" s="49">
+      <c r="V203" s="25">
         <v>160</v>
       </c>
     </row>
@@ -8085,10 +8018,10 @@
         <v>19</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D204" s="13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E204" s="9"/>
       <c r="F204" s="9"/>
@@ -8107,7 +8040,7 @@
       <c r="S204" s="13"/>
       <c r="T204" s="9"/>
       <c r="U204" s="9"/>
-      <c r="V204" s="49">
+      <c r="V204" s="25">
         <v>168</v>
       </c>
     </row>
@@ -8119,7 +8052,7 @@
         <v>10</v>
       </c>
       <c r="D205" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E205" s="9"/>
       <c r="F205" s="9"/>
@@ -8138,7 +8071,7 @@
       <c r="S205" s="13"/>
       <c r="T205" s="9"/>
       <c r="U205" s="9"/>
-      <c r="V205" s="49">
+      <c r="V205" s="25">
         <v>172</v>
       </c>
     </row>
@@ -8150,7 +8083,7 @@
         <v>11</v>
       </c>
       <c r="D206" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E206" s="9"/>
       <c r="F206" s="9"/>
@@ -8169,7 +8102,7 @@
       <c r="S206" s="13"/>
       <c r="T206" s="9"/>
       <c r="U206" s="9"/>
-      <c r="V206" s="49">
+      <c r="V206" s="25">
         <v>173</v>
       </c>
     </row>
@@ -8181,7 +8114,7 @@
         <v>12</v>
       </c>
       <c r="D207" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E207" s="9"/>
       <c r="F207" s="9"/>
@@ -8200,7 +8133,7 @@
       <c r="S207" s="13"/>
       <c r="T207" s="9"/>
       <c r="U207" s="9"/>
-      <c r="V207" s="49">
+      <c r="V207" s="25">
         <v>170</v>
       </c>
     </row>
@@ -8212,7 +8145,7 @@
         <v>13</v>
       </c>
       <c r="D208" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E208" s="9"/>
       <c r="F208" s="9"/>
@@ -8231,7 +8164,7 @@
       <c r="S208" s="13"/>
       <c r="T208" s="9"/>
       <c r="U208" s="9"/>
-      <c r="V208" s="49">
+      <c r="V208" s="25">
         <v>161</v>
       </c>
     </row>
@@ -8243,7 +8176,7 @@
         <v>14</v>
       </c>
       <c r="D209" s="13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E209" s="9"/>
       <c r="F209" s="9"/>
@@ -8262,7 +8195,7 @@
       <c r="S209" s="13"/>
       <c r="T209" s="9"/>
       <c r="U209" s="9"/>
-      <c r="V209" s="49">
+      <c r="V209" s="25">
         <v>170</v>
       </c>
     </row>
@@ -8274,7 +8207,7 @@
         <v>1</v>
       </c>
       <c r="D210" s="13" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E210" s="9"/>
       <c r="F210" s="9"/>
@@ -8293,7 +8226,7 @@
       <c r="S210" s="13"/>
       <c r="T210" s="9"/>
       <c r="U210" s="9"/>
-      <c r="V210" s="49">
+      <c r="V210" s="25">
         <v>179</v>
       </c>
     </row>
@@ -8305,7 +8238,7 @@
         <v>2</v>
       </c>
       <c r="D211" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E211" s="9"/>
       <c r="F211" s="9"/>
@@ -8324,7 +8257,7 @@
       <c r="S211" s="13"/>
       <c r="T211" s="9"/>
       <c r="U211" s="9"/>
-      <c r="V211" s="49">
+      <c r="V211" s="25">
         <v>169</v>
       </c>
     </row>
@@ -8336,7 +8269,7 @@
         <v>3</v>
       </c>
       <c r="D212" s="13" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E212" s="9"/>
       <c r="F212" s="9"/>
@@ -8355,7 +8288,7 @@
       <c r="S212" s="13"/>
       <c r="T212" s="9"/>
       <c r="U212" s="9"/>
-      <c r="V212" s="49">
+      <c r="V212" s="25">
         <v>208</v>
       </c>
     </row>
@@ -8367,7 +8300,7 @@
         <v>4</v>
       </c>
       <c r="D213" s="13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E213" s="9"/>
       <c r="F213" s="9"/>
@@ -8386,7 +8319,7 @@
       <c r="S213" s="13"/>
       <c r="T213" s="9"/>
       <c r="U213" s="9"/>
-      <c r="V213" s="49">
+      <c r="V213" s="25">
         <v>205</v>
       </c>
     </row>
@@ -8398,7 +8331,7 @@
         <v>5</v>
       </c>
       <c r="D214" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E214" s="9"/>
       <c r="F214" s="9"/>
@@ -8417,7 +8350,7 @@
       <c r="S214" s="13"/>
       <c r="T214" s="9"/>
       <c r="U214" s="9"/>
-      <c r="V214" s="49">
+      <c r="V214" s="25">
         <v>156</v>
       </c>
     </row>
@@ -8429,7 +8362,7 @@
         <v>6</v>
       </c>
       <c r="D215" s="13" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E215" s="9"/>
       <c r="F215" s="9"/>
@@ -8448,7 +8381,7 @@
       <c r="S215" s="13"/>
       <c r="T215" s="9"/>
       <c r="U215" s="9"/>
-      <c r="V215" s="49">
+      <c r="V215" s="25">
         <v>179</v>
       </c>
     </row>
@@ -8460,7 +8393,7 @@
         <v>7</v>
       </c>
       <c r="D216" s="13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E216" s="9"/>
       <c r="F216" s="9"/>
@@ -8479,7 +8412,7 @@
       <c r="S216" s="13"/>
       <c r="T216" s="9"/>
       <c r="U216" s="9"/>
-      <c r="V216" s="49">
+      <c r="V216" s="25">
         <v>149</v>
       </c>
     </row>
@@ -8491,7 +8424,7 @@
         <v>8</v>
       </c>
       <c r="D217" s="13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E217" s="9"/>
       <c r="F217" s="9"/>
@@ -8510,7 +8443,7 @@
       <c r="S217" s="13"/>
       <c r="T217" s="9"/>
       <c r="U217" s="9"/>
-      <c r="V217" s="49">
+      <c r="V217" s="25">
         <v>176</v>
       </c>
     </row>
@@ -8522,7 +8455,7 @@
         <v>9</v>
       </c>
       <c r="D218" s="13" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E218" s="9"/>
       <c r="F218" s="9"/>
@@ -8541,7 +8474,7 @@
       <c r="S218" s="13"/>
       <c r="T218" s="9"/>
       <c r="U218" s="9"/>
-      <c r="V218" s="49">
+      <c r="V218" s="25">
         <v>162</v>
       </c>
     </row>
@@ -8553,7 +8486,7 @@
         <v>10</v>
       </c>
       <c r="D219" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E219" s="9"/>
       <c r="F219" s="9"/>
@@ -8572,7 +8505,7 @@
       <c r="S219" s="13"/>
       <c r="T219" s="9"/>
       <c r="U219" s="9"/>
-      <c r="V219" s="49">
+      <c r="V219" s="25">
         <v>186</v>
       </c>
     </row>
@@ -8584,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="D220" s="13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E220" s="9"/>
       <c r="F220" s="9"/>
@@ -8603,7 +8536,7 @@
       <c r="S220" s="13"/>
       <c r="T220" s="9"/>
       <c r="U220" s="9"/>
-      <c r="V220" s="49">
+      <c r="V220" s="25">
         <v>159</v>
       </c>
     </row>
@@ -8615,7 +8548,7 @@
         <v>2</v>
       </c>
       <c r="D221" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E221" s="9"/>
       <c r="F221" s="9"/>
@@ -8634,7 +8567,7 @@
       <c r="S221" s="13"/>
       <c r="T221" s="9"/>
       <c r="U221" s="9"/>
-      <c r="V221" s="49">
+      <c r="V221" s="25">
         <v>158</v>
       </c>
     </row>
@@ -8646,7 +8579,7 @@
         <v>3</v>
       </c>
       <c r="D222" s="13" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E222" s="9"/>
       <c r="F222" s="9"/>
@@ -8665,7 +8598,7 @@
       <c r="S222" s="13"/>
       <c r="T222" s="9"/>
       <c r="U222" s="9"/>
-      <c r="V222" s="49">
+      <c r="V222" s="25">
         <v>159</v>
       </c>
     </row>
@@ -8677,7 +8610,7 @@
         <v>4</v>
       </c>
       <c r="D223" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E223" s="9"/>
       <c r="F223" s="9"/>
@@ -8696,7 +8629,7 @@
       <c r="S223" s="13"/>
       <c r="T223" s="9"/>
       <c r="U223" s="9"/>
-      <c r="V223" s="49">
+      <c r="V223" s="25">
         <v>152</v>
       </c>
     </row>
@@ -8708,7 +8641,7 @@
         <v>5</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E224" s="9"/>
       <c r="F224" s="9"/>
@@ -8727,7 +8660,7 @@
       <c r="S224" s="13"/>
       <c r="T224" s="9"/>
       <c r="U224" s="9"/>
-      <c r="V224" s="49">
+      <c r="V224" s="25">
         <v>153</v>
       </c>
     </row>
@@ -8739,7 +8672,7 @@
         <v>6</v>
       </c>
       <c r="D225" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E225" s="9"/>
       <c r="F225" s="9"/>
@@ -8758,7 +8691,7 @@
       <c r="S225" s="13"/>
       <c r="T225" s="9"/>
       <c r="U225" s="9"/>
-      <c r="V225" s="49">
+      <c r="V225" s="25">
         <v>169</v>
       </c>
     </row>
@@ -8770,7 +8703,7 @@
         <v>7</v>
       </c>
       <c r="D226" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E226" s="9"/>
       <c r="F226" s="9"/>
@@ -8789,7 +8722,7 @@
       <c r="S226" s="13"/>
       <c r="T226" s="9"/>
       <c r="U226" s="9"/>
-      <c r="V226" s="49">
+      <c r="V226" s="25">
         <v>137</v>
       </c>
     </row>
@@ -8801,7 +8734,7 @@
         <v>8</v>
       </c>
       <c r="D227" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E227" s="9"/>
       <c r="F227" s="9"/>
@@ -8820,7 +8753,7 @@
       <c r="S227" s="13"/>
       <c r="T227" s="9"/>
       <c r="U227" s="9"/>
-      <c r="V227" s="49">
+      <c r="V227" s="25">
         <v>139</v>
       </c>
     </row>
@@ -8832,7 +8765,7 @@
         <v>9</v>
       </c>
       <c r="D228" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E228" s="9"/>
       <c r="F228" s="9"/>
@@ -8851,7 +8784,7 @@
       <c r="S228" s="13"/>
       <c r="T228" s="9"/>
       <c r="U228" s="9"/>
-      <c r="V228" s="49">
+      <c r="V228" s="25">
         <v>186</v>
       </c>
     </row>
@@ -8863,7 +8796,7 @@
         <v>10</v>
       </c>
       <c r="D229" s="13" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E229" s="9"/>
       <c r="F229" s="9"/>
@@ -8882,7 +8815,7 @@
       <c r="S229" s="13"/>
       <c r="T229" s="9"/>
       <c r="U229" s="9"/>
-      <c r="V229" s="49">
+      <c r="V229" s="25">
         <v>163</v>
       </c>
     </row>
@@ -8894,7 +8827,7 @@
         <v>11</v>
       </c>
       <c r="D230" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E230" s="9"/>
       <c r="F230" s="9"/>
@@ -8913,7 +8846,7 @@
       <c r="S230" s="13"/>
       <c r="T230" s="9"/>
       <c r="U230" s="9"/>
-      <c r="V230" s="49">
+      <c r="V230" s="25">
         <v>155</v>
       </c>
     </row>
@@ -8925,7 +8858,7 @@
         <v>12</v>
       </c>
       <c r="D231" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E231" s="9"/>
       <c r="F231" s="9"/>
@@ -8944,7 +8877,7 @@
       <c r="S231" s="13"/>
       <c r="T231" s="9"/>
       <c r="U231" s="9"/>
-      <c r="V231" s="49">
+      <c r="V231" s="25">
         <v>177</v>
       </c>
     </row>
@@ -8956,7 +8889,7 @@
         <v>13</v>
       </c>
       <c r="D232" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E232" s="9"/>
       <c r="F232" s="9"/>
@@ -8975,7 +8908,7 @@
       <c r="S232" s="13"/>
       <c r="T232" s="9"/>
       <c r="U232" s="9"/>
-      <c r="V232" s="49">
+      <c r="V232" s="25">
         <v>149</v>
       </c>
     </row>
@@ -8987,7 +8920,7 @@
         <v>14</v>
       </c>
       <c r="D233" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E233" s="9"/>
       <c r="F233" s="9"/>
@@ -9006,7 +8939,7 @@
       <c r="S233" s="13"/>
       <c r="T233" s="9"/>
       <c r="U233" s="9"/>
-      <c r="V233" s="49">
+      <c r="V233" s="25">
         <v>177</v>
       </c>
     </row>
@@ -9018,7 +8951,7 @@
         <v>15</v>
       </c>
       <c r="D234" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E234" s="9"/>
       <c r="F234" s="9"/>
@@ -9037,7 +8970,7 @@
       <c r="S234" s="13"/>
       <c r="T234" s="9"/>
       <c r="U234" s="9"/>
-      <c r="V234" s="49">
+      <c r="V234" s="25">
         <v>144</v>
       </c>
     </row>
@@ -9049,7 +8982,7 @@
         <v>16</v>
       </c>
       <c r="D235" s="13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E235" s="9"/>
       <c r="F235" s="9"/>
@@ -9068,7 +9001,7 @@
       <c r="S235" s="13"/>
       <c r="T235" s="9"/>
       <c r="U235" s="9"/>
-      <c r="V235" s="49">
+      <c r="V235" s="25">
         <v>158</v>
       </c>
     </row>
@@ -9080,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="D236" s="13" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E236" s="9"/>
       <c r="F236" s="9"/>
@@ -9099,7 +9032,7 @@
       <c r="S236" s="13"/>
       <c r="T236" s="9"/>
       <c r="U236" s="9"/>
-      <c r="V236" s="49">
+      <c r="V236" s="25">
         <v>172</v>
       </c>
     </row>
@@ -9111,7 +9044,7 @@
         <v>2</v>
       </c>
       <c r="D237" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E237" s="9"/>
       <c r="F237" s="9"/>
@@ -9130,7 +9063,7 @@
       <c r="S237" s="13"/>
       <c r="T237" s="9"/>
       <c r="U237" s="9"/>
-      <c r="V237" s="49">
+      <c r="V237" s="25">
         <v>149</v>
       </c>
     </row>
@@ -9142,7 +9075,7 @@
         <v>3</v>
       </c>
       <c r="D238" s="13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E238" s="9"/>
       <c r="F238" s="9"/>
@@ -9161,7 +9094,7 @@
       <c r="S238" s="13"/>
       <c r="T238" s="9"/>
       <c r="U238" s="9"/>
-      <c r="V238" s="49">
+      <c r="V238" s="25">
         <v>173</v>
       </c>
     </row>
@@ -9173,7 +9106,7 @@
         <v>4</v>
       </c>
       <c r="D239" s="13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E239" s="9"/>
       <c r="F239" s="9"/>
@@ -9192,7 +9125,7 @@
       <c r="S239" s="13"/>
       <c r="T239" s="9"/>
       <c r="U239" s="9"/>
-      <c r="V239" s="49">
+      <c r="V239" s="25">
         <v>183</v>
       </c>
     </row>
@@ -9204,7 +9137,7 @@
         <v>5</v>
       </c>
       <c r="D240" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E240" s="9"/>
       <c r="F240" s="9"/>
@@ -9223,7 +9156,7 @@
       <c r="S240" s="13"/>
       <c r="T240" s="9"/>
       <c r="U240" s="9"/>
-      <c r="V240" s="49">
+      <c r="V240" s="25">
         <v>145</v>
       </c>
     </row>
@@ -9235,7 +9168,7 @@
         <v>6</v>
       </c>
       <c r="D241" s="13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E241" s="9"/>
       <c r="F241" s="9"/>
@@ -9254,7 +9187,7 @@
       <c r="S241" s="13"/>
       <c r="T241" s="9"/>
       <c r="U241" s="9"/>
-      <c r="V241" s="49">
+      <c r="V241" s="25">
         <v>160</v>
       </c>
     </row>
@@ -9266,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="D242" s="13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E242" s="9"/>
       <c r="F242" s="9"/>
@@ -9285,7 +9218,7 @@
       <c r="S242" s="13"/>
       <c r="T242" s="9"/>
       <c r="U242" s="9"/>
-      <c r="V242" s="49">
+      <c r="V242" s="25">
         <v>201</v>
       </c>
     </row>
@@ -9297,7 +9230,7 @@
         <v>2</v>
       </c>
       <c r="D243" s="13" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E243" s="9"/>
       <c r="F243" s="9"/>
@@ -9316,7 +9249,7 @@
       <c r="S243" s="13"/>
       <c r="T243" s="9"/>
       <c r="U243" s="9"/>
-      <c r="V243" s="49">
+      <c r="V243" s="25">
         <v>196</v>
       </c>
     </row>
@@ -9328,7 +9261,7 @@
         <v>3</v>
       </c>
       <c r="D244" s="13" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E244" s="9"/>
       <c r="F244" s="9"/>
@@ -9347,7 +9280,7 @@
       <c r="S244" s="13"/>
       <c r="T244" s="9"/>
       <c r="U244" s="9"/>
-      <c r="V244" s="49">
+      <c r="V244" s="25">
         <v>215</v>
       </c>
     </row>
@@ -9359,7 +9292,7 @@
         <v>4</v>
       </c>
       <c r="D245" s="13" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E245" s="9"/>
       <c r="F245" s="9"/>
@@ -9378,7 +9311,7 @@
       <c r="S245" s="13"/>
       <c r="T245" s="9"/>
       <c r="U245" s="9"/>
-      <c r="V245" s="49">
+      <c r="V245" s="25">
         <v>173</v>
       </c>
     </row>
@@ -9390,7 +9323,7 @@
         <v>1</v>
       </c>
       <c r="D246" s="13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E246" s="9"/>
       <c r="F246" s="9"/>
@@ -9409,7 +9342,7 @@
       <c r="S246" s="13"/>
       <c r="T246" s="9"/>
       <c r="U246" s="9"/>
-      <c r="V246" s="49">
+      <c r="V246" s="25">
         <v>177</v>
       </c>
     </row>
@@ -9421,7 +9354,7 @@
         <v>2</v>
       </c>
       <c r="D247" s="13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E247" s="9"/>
       <c r="F247" s="9"/>
@@ -9440,7 +9373,7 @@
       <c r="S247" s="13"/>
       <c r="T247" s="9"/>
       <c r="U247" s="9"/>
-      <c r="V247" s="49">
+      <c r="V247" s="25">
         <v>139</v>
       </c>
     </row>
@@ -9452,7 +9385,7 @@
         <v>3</v>
       </c>
       <c r="D248" s="13" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E248" s="9"/>
       <c r="F248" s="9"/>
@@ -9471,7 +9404,7 @@
       <c r="S248" s="13"/>
       <c r="T248" s="9"/>
       <c r="U248" s="9"/>
-      <c r="V248" s="49">
+      <c r="V248" s="25">
         <v>173</v>
       </c>
     </row>
@@ -9483,7 +9416,7 @@
         <v>4</v>
       </c>
       <c r="D249" s="13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E249" s="9"/>
       <c r="F249" s="9"/>
@@ -9502,7 +9435,7 @@
       <c r="S249" s="13"/>
       <c r="T249" s="9"/>
       <c r="U249" s="9"/>
-      <c r="V249" s="49">
+      <c r="V249" s="25">
         <v>184</v>
       </c>
     </row>
@@ -9514,7 +9447,7 @@
         <v>5</v>
       </c>
       <c r="D250" s="13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E250" s="9"/>
       <c r="F250" s="9"/>
@@ -9533,7 +9466,7 @@
       <c r="S250" s="13"/>
       <c r="T250" s="9"/>
       <c r="U250" s="9"/>
-      <c r="V250" s="49">
+      <c r="V250" s="25">
         <v>175</v>
       </c>
     </row>
@@ -9545,7 +9478,7 @@
         <v>6</v>
       </c>
       <c r="D251" s="13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E251" s="9"/>
       <c r="F251" s="9"/>
@@ -9564,7 +9497,7 @@
       <c r="S251" s="13"/>
       <c r="T251" s="9"/>
       <c r="U251" s="9"/>
-      <c r="V251" s="49">
+      <c r="V251" s="25">
         <v>176</v>
       </c>
     </row>
@@ -9576,7 +9509,7 @@
         <v>7</v>
       </c>
       <c r="D252" s="13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E252" s="9"/>
       <c r="F252" s="9"/>
@@ -9595,7 +9528,7 @@
       <c r="S252" s="13"/>
       <c r="T252" s="9"/>
       <c r="U252" s="9"/>
-      <c r="V252" s="49">
+      <c r="V252" s="25">
         <v>163</v>
       </c>
     </row>
@@ -9607,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="D253" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E253" s="9"/>
       <c r="F253" s="9"/>
@@ -9626,7 +9559,7 @@
       <c r="S253" s="13"/>
       <c r="T253" s="9"/>
       <c r="U253" s="9"/>
-      <c r="V253" s="49">
+      <c r="V253" s="25">
         <v>202</v>
       </c>
     </row>
@@ -9638,7 +9571,7 @@
         <v>2</v>
       </c>
       <c r="D254" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E254" s="9"/>
       <c r="F254" s="9"/>
@@ -9657,7 +9590,7 @@
       <c r="S254" s="13"/>
       <c r="T254" s="9"/>
       <c r="U254" s="9"/>
-      <c r="V254" s="49">
+      <c r="V254" s="25">
         <v>215</v>
       </c>
     </row>
@@ -9669,7 +9602,7 @@
         <v>3</v>
       </c>
       <c r="D255" s="13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E255" s="9"/>
       <c r="F255" s="9"/>
@@ -9688,7 +9621,7 @@
       <c r="S255" s="13"/>
       <c r="T255" s="9"/>
       <c r="U255" s="9"/>
-      <c r="V255" s="49">
+      <c r="V255" s="25">
         <v>263</v>
       </c>
     </row>
@@ -9700,7 +9633,7 @@
         <v>4</v>
       </c>
       <c r="D256" s="13" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E256" s="9"/>
       <c r="F256" s="9"/>
@@ -9719,7 +9652,7 @@
       <c r="S256" s="13"/>
       <c r="T256" s="9"/>
       <c r="U256" s="9"/>
-      <c r="V256" s="49">
+      <c r="V256" s="25">
         <v>232</v>
       </c>
     </row>
@@ -9731,7 +9664,7 @@
         <v>5</v>
       </c>
       <c r="D257" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E257" s="9"/>
       <c r="F257" s="9"/>
@@ -9750,7 +9683,7 @@
       <c r="S257" s="13"/>
       <c r="T257" s="9"/>
       <c r="U257" s="9"/>
-      <c r="V257" s="49">
+      <c r="V257" s="25">
         <v>201</v>
       </c>
     </row>
@@ -9762,7 +9695,7 @@
         <v>6</v>
       </c>
       <c r="D258" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E258" s="9"/>
       <c r="F258" s="9"/>
@@ -9781,7 +9714,7 @@
       <c r="S258" s="13"/>
       <c r="T258" s="9"/>
       <c r="U258" s="9"/>
-      <c r="V258" s="49">
+      <c r="V258" s="25">
         <v>232</v>
       </c>
     </row>
@@ -9793,7 +9726,7 @@
         <v>7</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E259" s="9"/>
       <c r="F259" s="9"/>
@@ -9812,7 +9745,7 @@
       <c r="S259" s="13"/>
       <c r="T259" s="9"/>
       <c r="U259" s="9"/>
-      <c r="V259" s="49">
+      <c r="V259" s="25">
         <v>214</v>
       </c>
     </row>
@@ -9824,7 +9757,7 @@
         <v>1</v>
       </c>
       <c r="D260" s="13" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E260" s="9"/>
       <c r="F260" s="9"/>
@@ -9843,7 +9776,7 @@
       <c r="S260" s="13"/>
       <c r="T260" s="9"/>
       <c r="U260" s="9"/>
-      <c r="V260" s="49">
+      <c r="V260" s="25">
         <v>167</v>
       </c>
     </row>
@@ -9855,7 +9788,7 @@
         <v>2</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E261" s="9"/>
       <c r="F261" s="9"/>
@@ -9874,7 +9807,7 @@
       <c r="S261" s="13"/>
       <c r="T261" s="9"/>
       <c r="U261" s="9"/>
-      <c r="V261" s="49">
+      <c r="V261" s="25">
         <v>191</v>
       </c>
     </row>
@@ -9886,7 +9819,7 @@
         <v>3</v>
       </c>
       <c r="D262" s="13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E262" s="9"/>
       <c r="F262" s="9"/>
@@ -9905,7 +9838,7 @@
       <c r="S262" s="13"/>
       <c r="T262" s="9"/>
       <c r="U262" s="9"/>
-      <c r="V262" s="49">
+      <c r="V262" s="25">
         <v>165</v>
       </c>
     </row>
@@ -9917,7 +9850,7 @@
         <v>4</v>
       </c>
       <c r="D263" s="13" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E263" s="9"/>
       <c r="F263" s="9"/>
@@ -9936,7 +9869,7 @@
       <c r="S263" s="13"/>
       <c r="T263" s="9"/>
       <c r="U263" s="9"/>
-      <c r="V263" s="49">
+      <c r="V263" s="25">
         <v>167</v>
       </c>
     </row>
@@ -9948,7 +9881,7 @@
         <v>5</v>
       </c>
       <c r="D264" s="13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E264" s="9"/>
       <c r="F264" s="9"/>
@@ -9967,7 +9900,7 @@
       <c r="S264" s="13"/>
       <c r="T264" s="9"/>
       <c r="U264" s="9"/>
-      <c r="V264" s="49">
+      <c r="V264" s="25">
         <v>184</v>
       </c>
     </row>
@@ -9979,7 +9912,7 @@
         <v>6</v>
       </c>
       <c r="D265" s="13" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E265" s="9"/>
       <c r="F265" s="9"/>
@@ -9998,7 +9931,7 @@
       <c r="S265" s="13"/>
       <c r="T265" s="9"/>
       <c r="U265" s="9"/>
-      <c r="V265" s="49">
+      <c r="V265" s="25">
         <v>173</v>
       </c>
     </row>
@@ -10010,7 +9943,7 @@
         <v>7</v>
       </c>
       <c r="D266" s="13" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E266" s="9"/>
       <c r="F266" s="9"/>
@@ -10029,19 +9962,19 @@
       <c r="S266" s="13"/>
       <c r="T266" s="9"/>
       <c r="U266" s="9"/>
-      <c r="V266" s="49">
+      <c r="V266" s="25">
         <v>145</v>
       </c>
     </row>
     <row r="267" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B267" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C267" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E267" s="9"/>
       <c r="F267" s="9"/>
@@ -10060,19 +9993,19 @@
       <c r="S267" s="13"/>
       <c r="T267" s="9"/>
       <c r="U267" s="9"/>
-      <c r="V267" s="49">
+      <c r="V267" s="25">
         <v>141</v>
       </c>
     </row>
     <row r="268" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B268" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C268" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D268" s="13" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E268" s="9"/>
       <c r="F268" s="9"/>
@@ -10091,19 +10024,19 @@
       <c r="S268" s="13"/>
       <c r="T268" s="9"/>
       <c r="U268" s="9"/>
-      <c r="V268" s="49">
+      <c r="V268" s="25">
         <v>168</v>
       </c>
     </row>
     <row r="269" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B269" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C269" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E269" s="9"/>
       <c r="F269" s="9"/>
@@ -10122,19 +10055,19 @@
       <c r="S269" s="13"/>
       <c r="T269" s="9"/>
       <c r="U269" s="9"/>
-      <c r="V269" s="49">
+      <c r="V269" s="25">
         <v>132</v>
       </c>
     </row>
     <row r="270" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B270" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D270" s="13" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E270" s="9"/>
       <c r="F270" s="9"/>
@@ -10153,19 +10086,19 @@
       <c r="S270" s="13"/>
       <c r="T270" s="9"/>
       <c r="U270" s="9"/>
-      <c r="V270" s="49">
+      <c r="V270" s="25">
         <v>163</v>
       </c>
     </row>
     <row r="271" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B271" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E271" s="9"/>
       <c r="F271" s="9"/>
@@ -10184,19 +10117,19 @@
       <c r="S271" s="13"/>
       <c r="T271" s="9"/>
       <c r="U271" s="9"/>
-      <c r="V271" s="49">
+      <c r="V271" s="25">
         <v>168</v>
       </c>
     </row>
     <row r="272" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B272" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D272" s="13" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E272" s="9"/>
       <c r="F272" s="9"/>
@@ -10215,19 +10148,19 @@
       <c r="S272" s="13"/>
       <c r="T272" s="9"/>
       <c r="U272" s="9"/>
-      <c r="V272" s="49">
+      <c r="V272" s="25">
         <v>151</v>
       </c>
     </row>
     <row r="273" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B273" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C273" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E273" s="9"/>
       <c r="F273" s="9"/>
@@ -10246,19 +10179,19 @@
       <c r="S273" s="13"/>
       <c r="T273" s="9"/>
       <c r="U273" s="9"/>
-      <c r="V273" s="49">
+      <c r="V273" s="25">
         <v>172</v>
       </c>
     </row>
     <row r="274" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B274" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C274" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D274" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E274" s="9"/>
       <c r="F274" s="9"/>
@@ -10277,19 +10210,19 @@
       <c r="S274" s="13"/>
       <c r="T274" s="9"/>
       <c r="U274" s="9"/>
-      <c r="V274" s="49">
+      <c r="V274" s="25">
         <v>179</v>
       </c>
     </row>
     <row r="275" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B275" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C275" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D275" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E275" s="9"/>
       <c r="F275" s="9"/>
@@ -10308,19 +10241,19 @@
       <c r="S275" s="13"/>
       <c r="T275" s="9"/>
       <c r="U275" s="9"/>
-      <c r="V275" s="49">
+      <c r="V275" s="25">
         <v>201</v>
       </c>
     </row>
     <row r="276" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B276" s="19" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C276" s="19" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D276" s="20" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E276" s="9"/>
       <c r="F276" s="9"/>
@@ -10339,19 +10272,19 @@
       <c r="S276" s="13"/>
       <c r="T276" s="9"/>
       <c r="U276" s="9"/>
-      <c r="V276" s="49">
+      <c r="V276" s="25">
         <v>176</v>
       </c>
     </row>
     <row r="277" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B277" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C277" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E277" s="9"/>
       <c r="F277" s="9"/>
@@ -10370,19 +10303,19 @@
       <c r="S277" s="13"/>
       <c r="T277" s="9"/>
       <c r="U277" s="9"/>
-      <c r="V277" s="49">
+      <c r="V277" s="25">
         <v>188</v>
       </c>
     </row>
     <row r="278" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B278" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D278" s="13" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E278" s="9"/>
       <c r="F278" s="9"/>
@@ -10401,19 +10334,19 @@
       <c r="S278" s="13"/>
       <c r="T278" s="9"/>
       <c r="U278" s="9"/>
-      <c r="V278" s="49">
+      <c r="V278" s="25">
         <v>202</v>
       </c>
     </row>
     <row r="279" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B279" s="19" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D279" s="20" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E279" s="9"/>
       <c r="F279" s="9"/>
@@ -10432,19 +10365,19 @@
       <c r="S279" s="13"/>
       <c r="T279" s="9"/>
       <c r="U279" s="9"/>
-      <c r="V279" s="49">
+      <c r="V279" s="25">
         <v>165</v>
       </c>
     </row>
     <row r="280" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B280" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D280" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E280" s="9"/>
       <c r="F280" s="9"/>
@@ -10463,7 +10396,7 @@
       <c r="S280" s="13"/>
       <c r="T280" s="9"/>
       <c r="U280" s="9"/>
-      <c r="V280" s="49">
+      <c r="V280" s="25">
         <v>212</v>
       </c>
     </row>
@@ -10472,10 +10405,10 @@
         <v>29</v>
       </c>
       <c r="C281" s="18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D281" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E281" s="9"/>
       <c r="F281" s="9"/>
@@ -10494,7 +10427,7 @@
       <c r="S281" s="13"/>
       <c r="T281" s="9"/>
       <c r="U281" s="9"/>
-      <c r="V281" s="49">
+      <c r="V281" s="25">
         <v>177</v>
       </c>
     </row>
@@ -10503,10 +10436,10 @@
         <v>29</v>
       </c>
       <c r="C282" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D282" s="13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E282" s="9"/>
       <c r="F282" s="9"/>
@@ -10525,7 +10458,7 @@
       <c r="S282" s="13"/>
       <c r="T282" s="9"/>
       <c r="U282" s="9"/>
-      <c r="V282" s="49">
+      <c r="V282" s="25">
         <v>182</v>
       </c>
     </row>
@@ -10534,10 +10467,10 @@
         <v>29</v>
       </c>
       <c r="C283" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E283" s="9"/>
       <c r="F283" s="9"/>
@@ -10556,7 +10489,7 @@
       <c r="S283" s="13"/>
       <c r="T283" s="9"/>
       <c r="U283" s="9"/>
-      <c r="V283" s="49">
+      <c r="V283" s="25">
         <v>166</v>
       </c>
     </row>
@@ -10568,7 +10501,7 @@
         <v>1</v>
       </c>
       <c r="D284" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E284" s="9"/>
       <c r="F284" s="9"/>
@@ -10587,7 +10520,7 @@
       <c r="S284" s="13"/>
       <c r="T284" s="9"/>
       <c r="U284" s="9"/>
-      <c r="V284" s="49">
+      <c r="V284" s="25">
         <v>179</v>
       </c>
     </row>
@@ -10599,7 +10532,7 @@
         <v>2</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E285" s="9"/>
       <c r="F285" s="9"/>
@@ -10618,7 +10551,7 @@
       <c r="S285" s="13"/>
       <c r="T285" s="9"/>
       <c r="U285" s="9"/>
-      <c r="V285" s="49">
+      <c r="V285" s="25">
         <v>168</v>
       </c>
     </row>
@@ -10630,7 +10563,7 @@
         <v>3</v>
       </c>
       <c r="D286" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E286" s="9"/>
       <c r="F286" s="9"/>
@@ -10649,7 +10582,7 @@
       <c r="S286" s="13"/>
       <c r="T286" s="9"/>
       <c r="U286" s="9"/>
-      <c r="V286" s="49">
+      <c r="V286" s="25">
         <v>170</v>
       </c>
     </row>
@@ -10661,7 +10594,7 @@
         <v>4</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E287" s="9"/>
       <c r="F287" s="9"/>
@@ -10680,7 +10613,7 @@
       <c r="S287" s="13"/>
       <c r="T287" s="9"/>
       <c r="U287" s="9"/>
-      <c r="V287" s="49">
+      <c r="V287" s="25">
         <v>155</v>
       </c>
     </row>
@@ -10692,7 +10625,7 @@
         <v>5</v>
       </c>
       <c r="D288" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E288" s="9"/>
       <c r="F288" s="9"/>
@@ -10711,7 +10644,7 @@
       <c r="S288" s="13"/>
       <c r="T288" s="9"/>
       <c r="U288" s="9"/>
-      <c r="V288" s="49">
+      <c r="V288" s="25">
         <v>175</v>
       </c>
     </row>
@@ -10723,7 +10656,7 @@
         <v>6</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E289" s="9"/>
       <c r="F289" s="9"/>
@@ -10742,7 +10675,7 @@
       <c r="S289" s="13"/>
       <c r="T289" s="9"/>
       <c r="U289" s="9"/>
-      <c r="V289" s="49">
+      <c r="V289" s="25">
         <v>162</v>
       </c>
     </row>
@@ -10754,7 +10687,7 @@
         <v>7</v>
       </c>
       <c r="D290" s="13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E290" s="9"/>
       <c r="F290" s="9"/>
@@ -10773,7 +10706,7 @@
       <c r="S290" s="13"/>
       <c r="T290" s="9"/>
       <c r="U290" s="9"/>
-      <c r="V290" s="49">
+      <c r="V290" s="25">
         <v>184</v>
       </c>
     </row>
@@ -10785,7 +10718,7 @@
         <v>8</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E291" s="9"/>
       <c r="F291" s="9"/>
@@ -10804,7 +10737,7 @@
       <c r="S291" s="13"/>
       <c r="T291" s="9"/>
       <c r="U291" s="9"/>
-      <c r="V291" s="49">
+      <c r="V291" s="25">
         <v>187</v>
       </c>
     </row>
@@ -10816,7 +10749,7 @@
         <v>9</v>
       </c>
       <c r="D292" s="13" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E292" s="9"/>
       <c r="F292" s="9"/>
@@ -10835,7 +10768,7 @@
       <c r="S292" s="13"/>
       <c r="T292" s="9"/>
       <c r="U292" s="9"/>
-      <c r="V292" s="49">
+      <c r="V292" s="25">
         <v>163</v>
       </c>
     </row>
@@ -10847,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="D293" s="13" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E293" s="9"/>
       <c r="F293" s="9"/>
@@ -10866,7 +10799,7 @@
       <c r="S293" s="13"/>
       <c r="T293" s="9"/>
       <c r="U293" s="9"/>
-      <c r="V293" s="49">
+      <c r="V293" s="25">
         <v>195</v>
       </c>
     </row>
@@ -10878,7 +10811,7 @@
         <v>11</v>
       </c>
       <c r="D294" s="13" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E294" s="9"/>
       <c r="F294" s="9"/>
@@ -10897,7 +10830,7 @@
       <c r="S294" s="13"/>
       <c r="T294" s="9"/>
       <c r="U294" s="9"/>
-      <c r="V294" s="49">
+      <c r="V294" s="25">
         <v>165</v>
       </c>
     </row>
@@ -10909,7 +10842,7 @@
         <v>12</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E295" s="9"/>
       <c r="F295" s="9"/>
@@ -10928,7 +10861,7 @@
       <c r="S295" s="13"/>
       <c r="T295" s="9"/>
       <c r="U295" s="9"/>
-      <c r="V295" s="49">
+      <c r="V295" s="25">
         <v>152</v>
       </c>
     </row>
@@ -10940,7 +10873,7 @@
         <v>13</v>
       </c>
       <c r="D296" s="13" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E296" s="9"/>
       <c r="F296" s="9"/>
@@ -10959,7 +10892,7 @@
       <c r="S296" s="13"/>
       <c r="T296" s="9"/>
       <c r="U296" s="9"/>
-      <c r="V296" s="49">
+      <c r="V296" s="25">
         <v>156</v>
       </c>
     </row>
@@ -10971,7 +10904,7 @@
         <v>14</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E297" s="9"/>
       <c r="F297" s="9"/>
@@ -10990,7 +10923,7 @@
       <c r="S297" s="13"/>
       <c r="T297" s="9"/>
       <c r="U297" s="9"/>
-      <c r="V297" s="49">
+      <c r="V297" s="25">
         <v>167</v>
       </c>
     </row>
@@ -11002,7 +10935,7 @@
         <v>15</v>
       </c>
       <c r="D298" s="13" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E298" s="9"/>
       <c r="F298" s="9"/>
@@ -11021,7 +10954,7 @@
       <c r="S298" s="13"/>
       <c r="T298" s="9"/>
       <c r="U298" s="9"/>
-      <c r="V298" s="49">
+      <c r="V298" s="25">
         <v>155</v>
       </c>
     </row>
@@ -11033,7 +10966,7 @@
         <v>16</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E299" s="9"/>
       <c r="F299" s="9"/>
@@ -11052,7 +10985,7 @@
       <c r="S299" s="13"/>
       <c r="T299" s="9"/>
       <c r="U299" s="9"/>
-      <c r="V299" s="49">
+      <c r="V299" s="25">
         <v>170</v>
       </c>
     </row>
@@ -11064,7 +10997,7 @@
         <v>17</v>
       </c>
       <c r="D300" s="13" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E300" s="9"/>
       <c r="F300" s="9"/>
@@ -11083,7 +11016,7 @@
       <c r="S300" s="13"/>
       <c r="T300" s="9"/>
       <c r="U300" s="9"/>
-      <c r="V300" s="49">
+      <c r="V300" s="25">
         <v>184</v>
       </c>
     </row>
@@ -11095,7 +11028,7 @@
         <v>18</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E301" s="9"/>
       <c r="F301" s="9"/>
@@ -11114,7 +11047,7 @@
       <c r="S301" s="13"/>
       <c r="T301" s="9"/>
       <c r="U301" s="9"/>
-      <c r="V301" s="49">
+      <c r="V301" s="25">
         <v>160</v>
       </c>
     </row>
@@ -11126,7 +11059,7 @@
         <v>19</v>
       </c>
       <c r="D302" s="13" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E302" s="9"/>
       <c r="F302" s="9"/>
@@ -11145,7 +11078,7 @@
       <c r="S302" s="9"/>
       <c r="T302" s="9"/>
       <c r="U302" s="9"/>
-      <c r="V302" s="49">
+      <c r="V302" s="25">
         <v>168</v>
       </c>
     </row>
@@ -11157,7 +11090,7 @@
         <v>1</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E303" s="9"/>
       <c r="F303" s="9"/>
@@ -11176,7 +11109,7 @@
       <c r="S303" s="9"/>
       <c r="T303" s="9"/>
       <c r="U303" s="9"/>
-      <c r="V303" s="49">
+      <c r="V303" s="25">
         <v>139</v>
       </c>
     </row>
@@ -11188,7 +11121,7 @@
         <v>2</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E304" s="9"/>
       <c r="F304" s="9"/>
@@ -11207,7 +11140,7 @@
       <c r="S304" s="9"/>
       <c r="T304" s="9"/>
       <c r="U304" s="9"/>
-      <c r="V304" s="49">
+      <c r="V304" s="25">
         <v>161</v>
       </c>
     </row>
@@ -11219,7 +11152,7 @@
         <v>3</v>
       </c>
       <c r="D305" s="13" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E305" s="9"/>
       <c r="F305" s="9"/>
@@ -11238,7 +11171,7 @@
       <c r="S305" s="9"/>
       <c r="T305" s="9"/>
       <c r="U305" s="9"/>
-      <c r="V305" s="49">
+      <c r="V305" s="25">
         <v>155</v>
       </c>
     </row>
@@ -11250,7 +11183,7 @@
         <v>4</v>
       </c>
       <c r="D306" s="13" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E306" s="9"/>
       <c r="F306" s="9"/>
@@ -11269,7 +11202,7 @@
       <c r="S306" s="9"/>
       <c r="T306" s="9"/>
       <c r="U306" s="9"/>
-      <c r="V306" s="49">
+      <c r="V306" s="25">
         <v>155</v>
       </c>
     </row>
@@ -11281,7 +11214,7 @@
         <v>5</v>
       </c>
       <c r="D307" s="13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E307" s="9"/>
       <c r="F307" s="9"/>
@@ -11300,7 +11233,7 @@
       <c r="S307" s="9"/>
       <c r="T307" s="9"/>
       <c r="U307" s="9"/>
-      <c r="V307" s="49">
+      <c r="V307" s="25">
         <v>154</v>
       </c>
     </row>
@@ -11312,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E308" s="9"/>
       <c r="F308" s="9"/>
@@ -11331,7 +11264,7 @@
       <c r="S308" s="9"/>
       <c r="T308" s="9"/>
       <c r="U308" s="9"/>
-      <c r="V308" s="49">
+      <c r="V308" s="25">
         <v>147</v>
       </c>
     </row>
@@ -11343,7 +11276,7 @@
         <v>1</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E309" s="9"/>
       <c r="F309" s="9"/>
@@ -11362,7 +11295,7 @@
       <c r="S309" s="9"/>
       <c r="T309" s="9"/>
       <c r="U309" s="9"/>
-      <c r="V309" s="49">
+      <c r="V309" s="25">
         <v>200</v>
       </c>
     </row>
@@ -11374,7 +11307,7 @@
         <v>2</v>
       </c>
       <c r="D310" s="13" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E310" s="9"/>
       <c r="F310" s="9"/>
@@ -11393,7 +11326,7 @@
       <c r="S310" s="9"/>
       <c r="T310" s="9"/>
       <c r="U310" s="9"/>
-      <c r="V310" s="49">
+      <c r="V310" s="25">
         <v>235</v>
       </c>
     </row>
@@ -11405,7 +11338,7 @@
         <v>3</v>
       </c>
       <c r="D311" s="13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E311" s="9"/>
       <c r="F311" s="9"/>
@@ -11424,7 +11357,7 @@
       <c r="S311" s="9"/>
       <c r="T311" s="9"/>
       <c r="U311" s="9"/>
-      <c r="V311" s="49">
+      <c r="V311" s="25">
         <v>198</v>
       </c>
     </row>
@@ -11436,7 +11369,7 @@
         <v>4</v>
       </c>
       <c r="D312" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E312" s="9"/>
       <c r="F312" s="9"/>
@@ -11455,12 +11388,28 @@
       <c r="S312" s="9"/>
       <c r="T312" s="9"/>
       <c r="U312" s="9"/>
-      <c r="V312" s="49">
+      <c r="V312" s="25">
         <v>168</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="U10:U12"/>
+    <mergeCell ref="C2:U2"/>
+    <mergeCell ref="C3:U3"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="C5:S5"/>
     <mergeCell ref="V11:V12"/>
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="B10:B11"/>
@@ -11477,22 +11426,6 @@
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="B9:U9"/>
     <mergeCell ref="T10:T12"/>
-    <mergeCell ref="U10:U12"/>
-    <mergeCell ref="C2:U2"/>
-    <mergeCell ref="C3:U3"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="C5:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
